--- a/ComponentesMetodologicos/Normalizacion..xlsx
+++ b/ComponentesMetodologicos/Normalizacion..xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GABRIEL\PROYECTO_CEREBRUM\ComponentesMetodologicos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrador\Desktop\Proyecto JEPL\PROYECTO_CEREBRUM\PROYECTO_CEREBRUM\ComponentesMetodologicos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E977B0E-76AD-414D-8D94-013864552261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8089D4A-FD02-4327-8293-C86B702D1EB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,14 +28,17 @@
   </definedNames>
   <calcPr calcId="0"/>
   <customWorkbookViews>
+    <customWorkbookView name="Tabla5 filter view" guid="{626D8D2F-B7BD-49F0-B146-21AFFE642FF9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Tabla1 filter view" guid="{4BE0AE49-5167-486F-A74B-07AF5BFCAA2A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Tabla11 filter view" guid="{5BA99981-AF65-4323-B2F8-5F691FA1504F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Tabla3 filter view" guid="{7812FD8C-0E59-45E2-87A2-7698E6BE27A1}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
+    <customWorkbookView name="Tabla4 filter view" guid="{D65A4ACE-247C-439E-AEA8-2EA75470FCA5}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
     <customWorkbookView name="Tabla2 filter view" guid="{E35139AA-24E9-4A62-81CA-588D087135E4}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Tabla4 filter view" guid="{D65A4ACE-247C-439E-AEA8-2EA75470FCA5}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Tabla3 filter view" guid="{7812FD8C-0E59-45E2-87A2-7698E6BE27A1}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Tabla11 filter view" guid="{5BA99981-AF65-4323-B2F8-5F691FA1504F}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Tabla1 filter view" guid="{4BE0AE49-5167-486F-A74B-07AF5BFCAA2A}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
-    <customWorkbookView name="Tabla5 filter view" guid="{626D8D2F-B7BD-49F0-B146-21AFFE642FF9}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
   </customWorkbookViews>
   <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="PXevnmi5tJLOzOgUdzv8EA5xCRRRbAkw7i4s/mkcrlY="/>
     </ext>
@@ -3626,49 +3629,12 @@
     <xf numFmtId="0" fontId="1" fillId="25" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="25" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3688,33 +3654,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="26" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="21" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3759,14 +3698,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="21" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3783,20 +3716,90 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3804,61 +3807,48 @@
   </cellStyles>
   <dxfs count="54">
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
+        <left/>
+        <right style="thin">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -3921,45 +3911,57 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
+        <right/>
         <top style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </top>
         <bottom style="thin">
-          <color rgb="FF000000"/>
+          <color indexed="64"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -4521,8 +4523,8 @@
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E45A90DF-88C5-4874-AC06-8852E5D14C3B}" name="Tabla25" displayName="Tabla25" ref="F24:G43">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{1EFCE341-C496-4A2B-BA1F-90A92678F278}" name="ID_Correo" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{8E7A50D2-1C3B-4BAA-95B2-B8A8113969CD}" name="ID_Cuenta" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{1EFCE341-C496-4A2B-BA1F-90A92678F278}" name="ID_Correo" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{8E7A50D2-1C3B-4BAA-95B2-B8A8113969CD}" name="ID_Cuenta" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="2FN-style 10" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4531,8 +4533,8 @@
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{02D9B4DA-CFF4-4A56-954A-5CB19BD13D16}" name="Tema6" displayName="Tema6" ref="N2:O22">
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{846C0EF0-62EC-4EF7-8F9F-B8CEAE12C6EE}" name="id_tema" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{A83FC18F-27B3-4430-A790-76FE38AAF40E}" name="id_materia" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{846C0EF0-62EC-4EF7-8F9F-B8CEAE12C6EE}" name="id_tema" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{A83FC18F-27B3-4430-A790-76FE38AAF40E}" name="id_materia" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="2FN-style 11" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4603,9 +4605,9 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3501149D-CD1B-4F1D-8A05-9D2360D8F5BE}" name="Table_12" displayName="Table_12" ref="O26:O61" headerRowCount="0" headerRowDxfId="1" totalsRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3501149D-CD1B-4F1D-8A05-9D2360D8F5BE}" name="Table_12" displayName="Table_12" ref="O26:O61" headerRowCount="0" headerRowDxfId="7" totalsRowDxfId="6">
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{0E6E64C9-30D5-42D5-9D67-6EA5FD7DC424}" name="Column1" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{0E6E64C9-30D5-42D5-9D67-6EA5FD7DC424}" name="Column1" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="2FN-style 6" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4625,7 +4627,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6DAF817B-DEB7-430B-A38E-CE7DEEABC1E8}" name="Tabla14" displayName="Tabla14" ref="F2:G21">
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{F1DE868E-2912-47C1-9513-223344A5870F}" name="ID_Telefono"/>
-    <tableColumn id="3" xr3:uid="{9FE4E02F-05A7-4460-B55A-3AB71F98A2F4}" name="ID_Cuenta" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{9FE4E02F-05A7-4460-B55A-3AB71F98A2F4}" name="ID_Cuenta" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="2FN-style 9" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -36430,33 +36432,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A1" s="178" t="s">
+      <c r="A1" s="199" t="s">
         <v>688</v>
       </c>
-      <c r="B1" s="179"/>
-      <c r="C1" s="179"/>
-      <c r="D1" s="179"/>
-      <c r="E1" s="179"/>
-      <c r="F1" s="179"/>
-      <c r="G1" s="179"/>
-      <c r="H1" s="180"/>
-      <c r="N1" s="161" t="s">
+      <c r="B1" s="200"/>
+      <c r="C1" s="200"/>
+      <c r="D1" s="200"/>
+      <c r="E1" s="200"/>
+      <c r="F1" s="200"/>
+      <c r="G1" s="200"/>
+      <c r="H1" s="201"/>
+      <c r="N1" s="191" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="182"/>
-      <c r="P1" s="183"/>
-      <c r="R1" s="184" t="s">
+      <c r="O1" s="192"/>
+      <c r="P1" s="193"/>
+      <c r="R1" s="194" t="s">
         <v>417</v>
       </c>
-      <c r="S1" s="184"/>
-      <c r="T1" s="184"/>
-      <c r="V1" s="155" t="s">
+      <c r="S1" s="194"/>
+      <c r="T1" s="194"/>
+      <c r="V1" s="188" t="s">
         <v>418</v>
       </c>
-      <c r="W1" s="204"/>
-      <c r="X1" s="204"/>
-      <c r="Y1" s="204"/>
-      <c r="Z1" s="214"/>
+      <c r="W1" s="189"/>
+      <c r="X1" s="189"/>
+      <c r="Y1" s="189"/>
+      <c r="Z1" s="190"/>
     </row>
     <row r="2" spans="1:26">
       <c r="A2" s="152" t="s">
@@ -36471,22 +36473,22 @@
       <c r="D2" s="152" t="s">
         <v>410</v>
       </c>
-      <c r="E2" s="169" t="s">
+      <c r="E2" s="156" t="s">
         <v>411</v>
       </c>
       <c r="F2" s="152" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="170" t="s">
+      <c r="G2" s="157" t="s">
         <v>412</v>
       </c>
       <c r="H2" s="152" t="s">
         <v>689</v>
       </c>
-      <c r="J2" s="153" t="s">
+      <c r="J2" s="202" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="154"/>
+      <c r="K2" s="203"/>
       <c r="N2" s="111" t="s">
         <v>549</v>
       </c>
@@ -36522,28 +36524,28 @@
       </c>
     </row>
     <row r="3" spans="1:26">
-      <c r="A3" s="171" t="s">
+      <c r="A3" s="158" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="172" t="s">
+      <c r="B3" s="159" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="172" t="s">
+      <c r="C3" s="159" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="173">
+      <c r="D3" s="160">
         <v>39521</v>
       </c>
-      <c r="E3" s="174" t="s">
+      <c r="E3" s="161" t="s">
         <v>415</v>
       </c>
-      <c r="F3" s="172">
+      <c r="F3" s="159">
         <v>1001001001</v>
       </c>
-      <c r="G3" s="175" t="s">
+      <c r="G3" s="162" t="s">
         <v>416</v>
       </c>
-      <c r="H3" s="172" t="s">
+      <c r="H3" s="159" t="s">
         <v>501</v>
       </c>
       <c r="J3" s="126" t="s">
@@ -36587,28 +36589,28 @@
       </c>
     </row>
     <row r="4" spans="1:26">
-      <c r="A4" s="171" t="s">
+      <c r="A4" s="158" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="172" t="s">
+      <c r="B4" s="159" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="172" t="s">
+      <c r="C4" s="159" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="173">
+      <c r="D4" s="160">
         <v>39521</v>
       </c>
-      <c r="E4" s="174" t="s">
+      <c r="E4" s="161" t="s">
         <v>415</v>
       </c>
-      <c r="F4" s="172">
+      <c r="F4" s="159">
         <v>1001001001</v>
       </c>
-      <c r="G4" s="175" t="s">
+      <c r="G4" s="162" t="s">
         <v>416</v>
       </c>
-      <c r="H4" s="172" t="s">
+      <c r="H4" s="159" t="s">
         <v>512</v>
       </c>
       <c r="J4" s="128" t="s">
@@ -36652,28 +36654,28 @@
       </c>
     </row>
     <row r="5" spans="1:26">
-      <c r="A5" s="171" t="s">
+      <c r="A5" s="158" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="172" t="s">
+      <c r="B5" s="159" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="172" t="s">
+      <c r="C5" s="159" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="173">
+      <c r="D5" s="160">
         <v>39521</v>
       </c>
-      <c r="E5" s="174" t="s">
+      <c r="E5" s="161" t="s">
         <v>415</v>
       </c>
-      <c r="F5" s="172">
+      <c r="F5" s="159">
         <v>1001001001</v>
       </c>
-      <c r="G5" s="175" t="s">
+      <c r="G5" s="162" t="s">
         <v>416</v>
       </c>
-      <c r="H5" s="172" t="s">
+      <c r="H5" s="159" t="s">
         <v>518</v>
       </c>
       <c r="J5" s="130" t="s">
@@ -36717,28 +36719,28 @@
       </c>
     </row>
     <row r="6" spans="1:26">
-      <c r="A6" s="171" t="s">
+      <c r="A6" s="158" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="172" t="s">
+      <c r="B6" s="159" t="s">
         <v>63</v>
       </c>
-      <c r="C6" s="172" t="s">
+      <c r="C6" s="159" t="s">
         <v>66</v>
       </c>
-      <c r="D6" s="173">
+      <c r="D6" s="160">
         <v>38498</v>
       </c>
-      <c r="E6" s="174" t="s">
+      <c r="E6" s="161" t="s">
         <v>420</v>
       </c>
-      <c r="F6" s="172">
+      <c r="F6" s="159">
         <v>1001001002</v>
       </c>
-      <c r="G6" s="175" t="s">
+      <c r="G6" s="162" t="s">
         <v>421</v>
       </c>
-      <c r="H6" s="172" t="s">
+      <c r="H6" s="159" t="s">
         <v>518</v>
       </c>
       <c r="J6" s="128" t="s">
@@ -36782,28 +36784,28 @@
       </c>
     </row>
     <row r="7" spans="1:26">
-      <c r="A7" s="171" t="s">
+      <c r="A7" s="158" t="s">
         <v>62</v>
       </c>
-      <c r="B7" s="172" t="s">
+      <c r="B7" s="159" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="172" t="s">
+      <c r="C7" s="159" t="s">
         <v>66</v>
       </c>
-      <c r="D7" s="173">
+      <c r="D7" s="160">
         <v>38498</v>
       </c>
-      <c r="E7" s="174" t="s">
+      <c r="E7" s="161" t="s">
         <v>420</v>
       </c>
-      <c r="F7" s="172">
+      <c r="F7" s="159">
         <v>1001001002</v>
       </c>
-      <c r="G7" s="175" t="s">
+      <c r="G7" s="162" t="s">
         <v>421</v>
       </c>
-      <c r="H7" s="172" t="s">
+      <c r="H7" s="159" t="s">
         <v>507</v>
       </c>
       <c r="J7" s="132" t="s">
@@ -36847,28 +36849,28 @@
       </c>
     </row>
     <row r="8" spans="1:26">
-      <c r="A8" s="171" t="s">
+      <c r="A8" s="158" t="s">
         <v>98</v>
       </c>
-      <c r="B8" s="172" t="s">
+      <c r="B8" s="159" t="s">
         <v>101</v>
       </c>
-      <c r="C8" s="172" t="s">
+      <c r="C8" s="159" t="s">
         <v>103</v>
       </c>
-      <c r="D8" s="173">
+      <c r="D8" s="160">
         <v>37444</v>
       </c>
-      <c r="E8" s="174" t="s">
+      <c r="E8" s="161" t="s">
         <v>429</v>
       </c>
-      <c r="F8" s="172">
+      <c r="F8" s="159">
         <v>1001001003</v>
       </c>
-      <c r="G8" s="175" t="s">
+      <c r="G8" s="162" t="s">
         <v>430</v>
       </c>
-      <c r="H8" s="172" t="s">
+      <c r="H8" s="159" t="s">
         <v>512</v>
       </c>
       <c r="N8" s="103" t="s">
@@ -36906,34 +36908,34 @@
       </c>
     </row>
     <row r="9" spans="1:26">
-      <c r="A9" s="171" t="s">
+      <c r="A9" s="158" t="s">
         <v>98</v>
       </c>
-      <c r="B9" s="172" t="s">
+      <c r="B9" s="159" t="s">
         <v>101</v>
       </c>
-      <c r="C9" s="172" t="s">
+      <c r="C9" s="159" t="s">
         <v>103</v>
       </c>
-      <c r="D9" s="173">
+      <c r="D9" s="160">
         <v>37444</v>
       </c>
-      <c r="E9" s="174" t="s">
+      <c r="E9" s="161" t="s">
         <v>429</v>
       </c>
-      <c r="F9" s="172">
+      <c r="F9" s="159">
         <v>1001001003</v>
       </c>
-      <c r="G9" s="175" t="s">
+      <c r="G9" s="162" t="s">
         <v>430</v>
       </c>
-      <c r="H9" s="172" t="s">
+      <c r="H9" s="159" t="s">
         <v>501</v>
       </c>
-      <c r="J9" s="164" t="s">
+      <c r="J9" s="204" t="s">
         <v>492</v>
       </c>
-      <c r="K9" s="181"/>
+      <c r="K9" s="205"/>
       <c r="N9" s="103" t="s">
         <v>589</v>
       </c>
@@ -36969,28 +36971,28 @@
       </c>
     </row>
     <row r="10" spans="1:26">
-      <c r="A10" s="171" t="s">
+      <c r="A10" s="158" t="s">
         <v>98</v>
       </c>
-      <c r="B10" s="172" t="s">
+      <c r="B10" s="159" t="s">
         <v>101</v>
       </c>
-      <c r="C10" s="172" t="s">
+      <c r="C10" s="159" t="s">
         <v>103</v>
       </c>
-      <c r="D10" s="173">
+      <c r="D10" s="160">
         <v>37444</v>
       </c>
-      <c r="E10" s="174" t="s">
+      <c r="E10" s="161" t="s">
         <v>429</v>
       </c>
-      <c r="F10" s="172">
+      <c r="F10" s="159">
         <v>1001001003</v>
       </c>
-      <c r="G10" s="175" t="s">
+      <c r="G10" s="162" t="s">
         <v>430</v>
       </c>
-      <c r="H10" s="172" t="s">
+      <c r="H10" s="159" t="s">
         <v>507</v>
       </c>
       <c r="J10" s="112" t="s">
@@ -37034,28 +37036,28 @@
       </c>
     </row>
     <row r="11" spans="1:26">
-      <c r="A11" s="171" t="s">
+      <c r="A11" s="158" t="s">
         <v>165</v>
       </c>
-      <c r="B11" s="172" t="s">
+      <c r="B11" s="159" t="s">
         <v>166</v>
       </c>
-      <c r="C11" s="172" t="s">
+      <c r="C11" s="159" t="s">
         <v>167</v>
       </c>
-      <c r="D11" s="173">
+      <c r="D11" s="160">
         <v>38967</v>
       </c>
-      <c r="E11" s="174" t="s">
+      <c r="E11" s="161" t="s">
         <v>415</v>
       </c>
-      <c r="F11" s="172">
+      <c r="F11" s="159">
         <v>1001001004</v>
       </c>
-      <c r="G11" s="175" t="s">
+      <c r="G11" s="162" t="s">
         <v>436</v>
       </c>
-      <c r="H11" s="172" t="s">
+      <c r="H11" s="159" t="s">
         <v>501</v>
       </c>
       <c r="J11" s="3" t="s">
@@ -37099,28 +37101,28 @@
       </c>
     </row>
     <row r="12" spans="1:26">
-      <c r="A12" s="171" t="s">
+      <c r="A12" s="158" t="s">
         <v>165</v>
       </c>
-      <c r="B12" s="172" t="s">
+      <c r="B12" s="159" t="s">
         <v>166</v>
       </c>
-      <c r="C12" s="172" t="s">
+      <c r="C12" s="159" t="s">
         <v>167</v>
       </c>
-      <c r="D12" s="173">
+      <c r="D12" s="160">
         <v>38967</v>
       </c>
-      <c r="E12" s="174" t="s">
+      <c r="E12" s="161" t="s">
         <v>415</v>
       </c>
-      <c r="F12" s="172">
+      <c r="F12" s="159">
         <v>1001001004</v>
       </c>
-      <c r="G12" s="175" t="s">
+      <c r="G12" s="162" t="s">
         <v>436</v>
       </c>
-      <c r="H12" s="172" t="s">
+      <c r="H12" s="159" t="s">
         <v>512</v>
       </c>
       <c r="J12" s="3" t="s">
@@ -37164,28 +37166,28 @@
       </c>
     </row>
     <row r="13" spans="1:26">
-      <c r="A13" s="171" t="s">
+      <c r="A13" s="158" t="s">
         <v>197</v>
       </c>
-      <c r="B13" s="172" t="s">
+      <c r="B13" s="159" t="s">
         <v>198</v>
       </c>
-      <c r="C13" s="172" t="s">
+      <c r="C13" s="159" t="s">
         <v>199</v>
       </c>
-      <c r="D13" s="173">
+      <c r="D13" s="160">
         <v>38802</v>
       </c>
-      <c r="E13" s="174" t="s">
+      <c r="E13" s="161" t="s">
         <v>429</v>
       </c>
-      <c r="F13" s="172">
+      <c r="F13" s="159">
         <v>1001001005</v>
       </c>
-      <c r="G13" s="175" t="s">
+      <c r="G13" s="162" t="s">
         <v>442</v>
       </c>
-      <c r="H13" s="172" t="s">
+      <c r="H13" s="159" t="s">
         <v>518</v>
       </c>
       <c r="J13" s="3" t="s">
@@ -37229,28 +37231,28 @@
       </c>
     </row>
     <row r="14" spans="1:26">
-      <c r="A14" s="171" t="s">
+      <c r="A14" s="158" t="s">
         <v>197</v>
       </c>
-      <c r="B14" s="172" t="s">
+      <c r="B14" s="159" t="s">
         <v>198</v>
       </c>
-      <c r="C14" s="172" t="s">
+      <c r="C14" s="159" t="s">
         <v>199</v>
       </c>
-      <c r="D14" s="173">
+      <c r="D14" s="160">
         <v>38802</v>
       </c>
-      <c r="E14" s="174" t="s">
+      <c r="E14" s="161" t="s">
         <v>429</v>
       </c>
-      <c r="F14" s="172">
+      <c r="F14" s="159">
         <v>1001001005</v>
       </c>
-      <c r="G14" s="175" t="s">
+      <c r="G14" s="162" t="s">
         <v>442</v>
       </c>
-      <c r="H14" s="172" t="s">
+      <c r="H14" s="159" t="s">
         <v>518</v>
       </c>
       <c r="J14" s="3" t="s">
@@ -37294,28 +37296,28 @@
       </c>
     </row>
     <row r="15" spans="1:26">
-      <c r="A15" s="171" t="s">
+      <c r="A15" s="158" t="s">
         <v>197</v>
       </c>
-      <c r="B15" s="172" t="s">
+      <c r="B15" s="159" t="s">
         <v>198</v>
       </c>
-      <c r="C15" s="172" t="s">
+      <c r="C15" s="159" t="s">
         <v>199</v>
       </c>
-      <c r="D15" s="173">
+      <c r="D15" s="160">
         <v>38802</v>
       </c>
-      <c r="E15" s="174" t="s">
+      <c r="E15" s="161" t="s">
         <v>429</v>
       </c>
-      <c r="F15" s="172">
+      <c r="F15" s="159">
         <v>1001001005</v>
       </c>
-      <c r="G15" s="175" t="s">
+      <c r="G15" s="162" t="s">
         <v>442</v>
       </c>
-      <c r="H15" s="172" t="s">
+      <c r="H15" s="159" t="s">
         <v>507</v>
       </c>
       <c r="N15" s="103" t="s">
@@ -37353,35 +37355,35 @@
       </c>
     </row>
     <row r="16" spans="1:26">
-      <c r="A16" s="171" t="s">
+      <c r="A16" s="158" t="s">
         <v>234</v>
       </c>
-      <c r="B16" s="172" t="s">
+      <c r="B16" s="159" t="s">
         <v>236</v>
       </c>
-      <c r="C16" s="172" t="s">
+      <c r="C16" s="159" t="s">
         <v>237</v>
       </c>
-      <c r="D16" s="173">
+      <c r="D16" s="160">
         <v>35315</v>
       </c>
-      <c r="E16" s="174" t="s">
+      <c r="E16" s="161" t="s">
         <v>429</v>
       </c>
-      <c r="F16" s="172">
+      <c r="F16" s="159">
         <v>1001001006</v>
       </c>
-      <c r="G16" s="175" t="s">
+      <c r="G16" s="162" t="s">
         <v>430</v>
       </c>
-      <c r="H16" s="172" t="s">
+      <c r="H16" s="159" t="s">
         <v>501</v>
       </c>
-      <c r="J16" s="158" t="s">
+      <c r="J16" s="206" t="s">
         <v>11</v>
       </c>
-      <c r="K16" s="159"/>
-      <c r="L16" s="160"/>
+      <c r="K16" s="207"/>
+      <c r="L16" s="208"/>
       <c r="N16" s="103" t="s">
         <v>632</v>
       </c>
@@ -37417,28 +37419,28 @@
       </c>
     </row>
     <row r="17" spans="1:28">
-      <c r="A17" s="171" t="s">
+      <c r="A17" s="158" t="s">
         <v>234</v>
       </c>
-      <c r="B17" s="172" t="s">
+      <c r="B17" s="159" t="s">
         <v>236</v>
       </c>
-      <c r="C17" s="172" t="s">
+      <c r="C17" s="159" t="s">
         <v>237</v>
       </c>
-      <c r="D17" s="173">
+      <c r="D17" s="160">
         <v>35315</v>
       </c>
-      <c r="E17" s="174" t="s">
+      <c r="E17" s="161" t="s">
         <v>429</v>
       </c>
-      <c r="F17" s="172">
+      <c r="F17" s="159">
         <v>1001001006</v>
       </c>
-      <c r="G17" s="175" t="s">
+      <c r="G17" s="162" t="s">
         <v>430</v>
       </c>
-      <c r="H17" s="172" t="s">
+      <c r="H17" s="159" t="s">
         <v>501</v>
       </c>
       <c r="J17" s="111" t="s">
@@ -37485,28 +37487,28 @@
       </c>
     </row>
     <row r="18" spans="1:28">
-      <c r="A18" s="171" t="s">
+      <c r="A18" s="158" t="s">
         <v>261</v>
       </c>
-      <c r="B18" s="172" t="s">
+      <c r="B18" s="159" t="s">
         <v>264</v>
       </c>
-      <c r="C18" s="172" t="s">
+      <c r="C18" s="159" t="s">
         <v>23</v>
       </c>
-      <c r="D18" s="173">
+      <c r="D18" s="160">
         <v>42014</v>
       </c>
-      <c r="E18" s="174" t="s">
+      <c r="E18" s="161" t="s">
         <v>453</v>
       </c>
-      <c r="F18" s="172">
+      <c r="F18" s="159">
         <v>1001001007</v>
       </c>
-      <c r="G18" s="175" t="s">
+      <c r="G18" s="162" t="s">
         <v>454</v>
       </c>
-      <c r="H18" s="172" t="s">
+      <c r="H18" s="159" t="s">
         <v>501</v>
       </c>
       <c r="J18" s="103" t="s">
@@ -37553,28 +37555,28 @@
       </c>
     </row>
     <row r="19" spans="1:28">
-      <c r="A19" s="171" t="s">
+      <c r="A19" s="158" t="s">
         <v>261</v>
       </c>
-      <c r="B19" s="172" t="s">
+      <c r="B19" s="159" t="s">
         <v>264</v>
       </c>
-      <c r="C19" s="172" t="s">
+      <c r="C19" s="159" t="s">
         <v>23</v>
       </c>
-      <c r="D19" s="173">
+      <c r="D19" s="160">
         <v>42014</v>
       </c>
-      <c r="E19" s="174" t="s">
+      <c r="E19" s="161" t="s">
         <v>453</v>
       </c>
-      <c r="F19" s="172">
+      <c r="F19" s="159">
         <v>1001001007</v>
       </c>
-      <c r="G19" s="175" t="s">
+      <c r="G19" s="162" t="s">
         <v>454</v>
       </c>
-      <c r="H19" s="172" t="s">
+      <c r="H19" s="159" t="s">
         <v>518</v>
       </c>
       <c r="J19" s="103" t="s">
@@ -37621,28 +37623,28 @@
       </c>
     </row>
     <row r="20" spans="1:28">
-      <c r="A20" s="171" t="s">
+      <c r="A20" s="158" t="s">
         <v>261</v>
       </c>
-      <c r="B20" s="172" t="s">
+      <c r="B20" s="159" t="s">
         <v>264</v>
       </c>
-      <c r="C20" s="172" t="s">
+      <c r="C20" s="159" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="173">
+      <c r="D20" s="160">
         <v>42014</v>
       </c>
-      <c r="E20" s="174" t="s">
+      <c r="E20" s="161" t="s">
         <v>453</v>
       </c>
-      <c r="F20" s="172">
+      <c r="F20" s="159">
         <v>1001001007</v>
       </c>
-      <c r="G20" s="175" t="s">
+      <c r="G20" s="162" t="s">
         <v>454</v>
       </c>
-      <c r="H20" s="172" t="s">
+      <c r="H20" s="159" t="s">
         <v>512</v>
       </c>
       <c r="J20" s="103" t="s">
@@ -37689,28 +37691,28 @@
       </c>
     </row>
     <row r="21" spans="1:28" ht="15.75" customHeight="1">
-      <c r="A21" s="171" t="s">
+      <c r="A21" s="158" t="s">
         <v>300</v>
       </c>
-      <c r="B21" s="172" t="s">
+      <c r="B21" s="159" t="s">
         <v>301</v>
       </c>
-      <c r="C21" s="172" t="s">
+      <c r="C21" s="159" t="s">
         <v>303</v>
       </c>
-      <c r="D21" s="173">
+      <c r="D21" s="160">
         <v>36768</v>
       </c>
-      <c r="E21" s="174" t="s">
+      <c r="E21" s="161" t="s">
         <v>453</v>
       </c>
-      <c r="F21" s="172">
+      <c r="F21" s="159">
         <v>1001001008</v>
       </c>
-      <c r="G21" s="175" t="s">
+      <c r="G21" s="162" t="s">
         <v>460</v>
       </c>
-      <c r="H21" s="172" t="s">
+      <c r="H21" s="159" t="s">
         <v>507</v>
       </c>
       <c r="J21" s="103" t="s">
@@ -37757,28 +37759,28 @@
       </c>
     </row>
     <row r="22" spans="1:28" ht="15.75" customHeight="1">
-      <c r="A22" s="171" t="s">
+      <c r="A22" s="158" t="s">
         <v>300</v>
       </c>
-      <c r="B22" s="172" t="s">
+      <c r="B22" s="159" t="s">
         <v>301</v>
       </c>
-      <c r="C22" s="172" t="s">
+      <c r="C22" s="159" t="s">
         <v>303</v>
       </c>
-      <c r="D22" s="173">
+      <c r="D22" s="160">
         <v>36768</v>
       </c>
-      <c r="E22" s="174" t="s">
+      <c r="E22" s="161" t="s">
         <v>453</v>
       </c>
-      <c r="F22" s="172">
+      <c r="F22" s="159">
         <v>1001001008</v>
       </c>
-      <c r="G22" s="175" t="s">
+      <c r="G22" s="162" t="s">
         <v>460</v>
       </c>
-      <c r="H22" s="172" t="s">
+      <c r="H22" s="159" t="s">
         <v>518</v>
       </c>
       <c r="J22" s="103" t="s">
@@ -37825,28 +37827,28 @@
       </c>
     </row>
     <row r="23" spans="1:28" ht="15.75" customHeight="1">
-      <c r="A23" s="171" t="s">
+      <c r="A23" s="158" t="s">
         <v>315</v>
       </c>
-      <c r="B23" s="172" t="s">
+      <c r="B23" s="159" t="s">
         <v>316</v>
       </c>
-      <c r="C23" s="172" t="s">
+      <c r="C23" s="159" t="s">
         <v>23</v>
       </c>
-      <c r="D23" s="173">
+      <c r="D23" s="160">
         <v>39644</v>
       </c>
-      <c r="E23" s="174" t="s">
+      <c r="E23" s="161" t="s">
         <v>453</v>
       </c>
-      <c r="F23" s="172">
+      <c r="F23" s="159">
         <v>1001001009</v>
       </c>
-      <c r="G23" s="175" t="s">
+      <c r="G23" s="162" t="s">
         <v>466</v>
       </c>
-      <c r="H23" s="172" t="s">
+      <c r="H23" s="159" t="s">
         <v>501</v>
       </c>
       <c r="J23" s="103" t="s">
@@ -37885,28 +37887,28 @@
       <c r="AB23" s="80"/>
     </row>
     <row r="24" spans="1:28" ht="15.75" customHeight="1">
-      <c r="A24" s="171" t="s">
+      <c r="A24" s="158" t="s">
         <v>315</v>
       </c>
-      <c r="B24" s="172" t="s">
+      <c r="B24" s="159" t="s">
         <v>316</v>
       </c>
-      <c r="C24" s="172" t="s">
+      <c r="C24" s="159" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="173">
+      <c r="D24" s="160">
         <v>39644</v>
       </c>
-      <c r="E24" s="174" t="s">
+      <c r="E24" s="161" t="s">
         <v>453</v>
       </c>
-      <c r="F24" s="172">
+      <c r="F24" s="159">
         <v>1001001009</v>
       </c>
-      <c r="G24" s="175" t="s">
+      <c r="G24" s="162" t="s">
         <v>466</v>
       </c>
-      <c r="H24" s="172" t="s">
+      <c r="H24" s="159" t="s">
         <v>501</v>
       </c>
       <c r="J24" s="103" t="s">
@@ -37918,11 +37920,11 @@
       <c r="L24" s="103" t="s">
         <v>346</v>
       </c>
-      <c r="N24" s="161" t="s">
+      <c r="N24" s="191" t="s">
         <v>6</v>
       </c>
-      <c r="O24" s="182"/>
-      <c r="P24" s="183"/>
+      <c r="O24" s="192"/>
+      <c r="P24" s="193"/>
       <c r="R24" s="39" t="s">
         <v>560</v>
       </c>
@@ -37949,28 +37951,28 @@
       </c>
     </row>
     <row r="25" spans="1:28" ht="15.75" customHeight="1">
-      <c r="A25" s="171" t="s">
+      <c r="A25" s="158" t="s">
         <v>315</v>
       </c>
-      <c r="B25" s="172" t="s">
+      <c r="B25" s="159" t="s">
         <v>316</v>
       </c>
-      <c r="C25" s="172" t="s">
+      <c r="C25" s="159" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="173">
+      <c r="D25" s="160">
         <v>39644</v>
       </c>
-      <c r="E25" s="174" t="s">
+      <c r="E25" s="161" t="s">
         <v>453</v>
       </c>
-      <c r="F25" s="172">
+      <c r="F25" s="159">
         <v>1001001009</v>
       </c>
-      <c r="G25" s="175" t="s">
+      <c r="G25" s="162" t="s">
         <v>466</v>
       </c>
-      <c r="H25" s="172" t="s">
+      <c r="H25" s="159" t="s">
         <v>512</v>
       </c>
       <c r="J25" s="103" t="s">
@@ -38017,28 +38019,28 @@
       </c>
     </row>
     <row r="26" spans="1:28" ht="15.75" customHeight="1">
-      <c r="A26" s="171" t="s">
+      <c r="A26" s="158" t="s">
         <v>325</v>
       </c>
-      <c r="B26" s="172" t="s">
+      <c r="B26" s="159" t="s">
         <v>326</v>
       </c>
-      <c r="C26" s="172" t="s">
+      <c r="C26" s="159" t="s">
         <v>327</v>
       </c>
-      <c r="D26" s="173">
+      <c r="D26" s="160">
         <v>39359</v>
       </c>
-      <c r="E26" s="174" t="s">
+      <c r="E26" s="161" t="s">
         <v>429</v>
       </c>
-      <c r="F26" s="172">
+      <c r="F26" s="159">
         <v>1001001010</v>
       </c>
-      <c r="G26" s="175" t="s">
+      <c r="G26" s="162" t="s">
         <v>430</v>
       </c>
-      <c r="H26" s="172" t="s">
+      <c r="H26" s="159" t="s">
         <v>512</v>
       </c>
       <c r="J26" s="103" t="s">
@@ -38085,28 +38087,28 @@
       </c>
     </row>
     <row r="27" spans="1:28" ht="15.75" customHeight="1">
-      <c r="A27" s="171" t="s">
+      <c r="A27" s="158" t="s">
         <v>325</v>
       </c>
-      <c r="B27" s="172" t="s">
+      <c r="B27" s="159" t="s">
         <v>326</v>
       </c>
-      <c r="C27" s="172" t="s">
+      <c r="C27" s="159" t="s">
         <v>327</v>
       </c>
-      <c r="D27" s="173">
+      <c r="D27" s="160">
         <v>39359</v>
       </c>
-      <c r="E27" s="174" t="s">
+      <c r="E27" s="161" t="s">
         <v>429</v>
       </c>
-      <c r="F27" s="172">
+      <c r="F27" s="159">
         <v>1001001010</v>
       </c>
-      <c r="G27" s="175" t="s">
+      <c r="G27" s="162" t="s">
         <v>430</v>
       </c>
-      <c r="H27" s="172" t="s">
+      <c r="H27" s="159" t="s">
         <v>518</v>
       </c>
       <c r="J27" s="103" t="s">
@@ -38153,28 +38155,28 @@
       </c>
     </row>
     <row r="28" spans="1:28" ht="15.75" customHeight="1">
-      <c r="A28" s="171" t="s">
+      <c r="A28" s="158" t="s">
         <v>325</v>
       </c>
-      <c r="B28" s="172" t="s">
+      <c r="B28" s="159" t="s">
         <v>326</v>
       </c>
-      <c r="C28" s="172" t="s">
+      <c r="C28" s="159" t="s">
         <v>327</v>
       </c>
-      <c r="D28" s="173">
+      <c r="D28" s="160">
         <v>39359</v>
       </c>
-      <c r="E28" s="174" t="s">
+      <c r="E28" s="161" t="s">
         <v>429</v>
       </c>
-      <c r="F28" s="172">
+      <c r="F28" s="159">
         <v>1001001010</v>
       </c>
-      <c r="G28" s="175" t="s">
+      <c r="G28" s="162" t="s">
         <v>430</v>
       </c>
-      <c r="H28" s="172" t="s">
+      <c r="H28" s="159" t="s">
         <v>512</v>
       </c>
       <c r="J28" s="103" t="s">
@@ -38221,28 +38223,28 @@
       </c>
     </row>
     <row r="29" spans="1:28" ht="15.75" customHeight="1">
-      <c r="A29" s="171" t="s">
+      <c r="A29" s="158" t="s">
         <v>338</v>
       </c>
-      <c r="B29" s="172" t="s">
+      <c r="B29" s="159" t="s">
         <v>339</v>
       </c>
-      <c r="C29" s="172" t="s">
+      <c r="C29" s="159" t="s">
         <v>340</v>
       </c>
-      <c r="D29" s="173">
+      <c r="D29" s="160">
         <v>39181</v>
       </c>
-      <c r="E29" s="174" t="s">
+      <c r="E29" s="161" t="s">
         <v>429</v>
       </c>
-      <c r="F29" s="172">
+      <c r="F29" s="159">
         <v>1001001011</v>
       </c>
-      <c r="G29" s="175" t="s">
+      <c r="G29" s="162" t="s">
         <v>471</v>
       </c>
-      <c r="H29" s="172" t="s">
+      <c r="H29" s="159" t="s">
         <v>507</v>
       </c>
       <c r="J29" s="103" t="s">
@@ -38289,28 +38291,28 @@
       </c>
     </row>
     <row r="30" spans="1:28" ht="15.75" customHeight="1">
-      <c r="A30" s="171" t="s">
+      <c r="A30" s="158" t="s">
         <v>338</v>
       </c>
-      <c r="B30" s="172" t="s">
+      <c r="B30" s="159" t="s">
         <v>339</v>
       </c>
-      <c r="C30" s="172" t="s">
+      <c r="C30" s="159" t="s">
         <v>340</v>
       </c>
-      <c r="D30" s="173">
+      <c r="D30" s="160">
         <v>39181</v>
       </c>
-      <c r="E30" s="174" t="s">
+      <c r="E30" s="161" t="s">
         <v>429</v>
       </c>
-      <c r="F30" s="172">
+      <c r="F30" s="159">
         <v>1001001011</v>
       </c>
-      <c r="G30" s="175" t="s">
+      <c r="G30" s="162" t="s">
         <v>471</v>
       </c>
-      <c r="H30" s="172" t="s">
+      <c r="H30" s="159" t="s">
         <v>501</v>
       </c>
       <c r="J30" s="103" t="s">
@@ -38357,28 +38359,28 @@
       </c>
     </row>
     <row r="31" spans="1:28" ht="15.75" customHeight="1">
-      <c r="A31" s="171" t="s">
+      <c r="A31" s="158" t="s">
         <v>348</v>
       </c>
-      <c r="B31" s="172" t="s">
+      <c r="B31" s="159" t="s">
         <v>349</v>
       </c>
-      <c r="C31" s="172" t="s">
+      <c r="C31" s="159" t="s">
         <v>350</v>
       </c>
-      <c r="D31" s="173">
+      <c r="D31" s="160">
         <v>46653</v>
       </c>
-      <c r="E31" s="174" t="s">
+      <c r="E31" s="161" t="s">
         <v>429</v>
       </c>
-      <c r="F31" s="172">
+      <c r="F31" s="159">
         <v>1001001012</v>
       </c>
-      <c r="G31" s="175" t="s">
+      <c r="G31" s="162" t="s">
         <v>466</v>
       </c>
-      <c r="H31" s="172" t="s">
+      <c r="H31" s="159" t="s">
         <v>501</v>
       </c>
       <c r="J31" s="103" t="s">
@@ -38425,28 +38427,28 @@
       </c>
     </row>
     <row r="32" spans="1:28" ht="15.75" customHeight="1">
-      <c r="A32" s="171" t="s">
+      <c r="A32" s="158" t="s">
         <v>348</v>
       </c>
-      <c r="B32" s="172" t="s">
+      <c r="B32" s="159" t="s">
         <v>349</v>
       </c>
-      <c r="C32" s="172" t="s">
+      <c r="C32" s="159" t="s">
         <v>350</v>
       </c>
-      <c r="D32" s="173">
+      <c r="D32" s="160">
         <v>46653</v>
       </c>
-      <c r="E32" s="174" t="s">
+      <c r="E32" s="161" t="s">
         <v>429</v>
       </c>
-      <c r="F32" s="172">
+      <c r="F32" s="159">
         <v>1001001012</v>
       </c>
-      <c r="G32" s="175" t="s">
+      <c r="G32" s="162" t="s">
         <v>466</v>
       </c>
-      <c r="H32" s="172" t="s">
+      <c r="H32" s="159" t="s">
         <v>512</v>
       </c>
       <c r="J32" s="103" t="s">
@@ -38493,28 +38495,28 @@
       </c>
     </row>
     <row r="33" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A33" s="171" t="s">
+      <c r="A33" s="158" t="s">
         <v>348</v>
       </c>
-      <c r="B33" s="172" t="s">
+      <c r="B33" s="159" t="s">
         <v>349</v>
       </c>
-      <c r="C33" s="172" t="s">
+      <c r="C33" s="159" t="s">
         <v>350</v>
       </c>
-      <c r="D33" s="173">
+      <c r="D33" s="160">
         <v>46653</v>
       </c>
-      <c r="E33" s="174" t="s">
+      <c r="E33" s="161" t="s">
         <v>429</v>
       </c>
-      <c r="F33" s="172">
+      <c r="F33" s="159">
         <v>1001001012</v>
       </c>
-      <c r="G33" s="175" t="s">
+      <c r="G33" s="162" t="s">
         <v>466</v>
       </c>
-      <c r="H33" s="172" t="s">
+      <c r="H33" s="159" t="s">
         <v>507</v>
       </c>
       <c r="J33" s="103" t="s">
@@ -38561,28 +38563,28 @@
       </c>
     </row>
     <row r="34" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A34" s="171" t="s">
+      <c r="A34" s="158" t="s">
         <v>356</v>
       </c>
-      <c r="B34" s="172" t="s">
+      <c r="B34" s="159" t="s">
         <v>357</v>
       </c>
-      <c r="C34" s="172" t="s">
+      <c r="C34" s="159" t="s">
         <v>358</v>
       </c>
-      <c r="D34" s="173">
+      <c r="D34" s="160">
         <v>37048</v>
       </c>
-      <c r="E34" s="174" t="s">
+      <c r="E34" s="161" t="s">
         <v>429</v>
       </c>
-      <c r="F34" s="172">
+      <c r="F34" s="159">
         <v>1001001013</v>
       </c>
-      <c r="G34" s="175" t="s">
+      <c r="G34" s="162" t="s">
         <v>430</v>
       </c>
-      <c r="H34" s="172" t="s">
+      <c r="H34" s="159" t="s">
         <v>518</v>
       </c>
       <c r="J34" s="103" t="s">
@@ -38629,28 +38631,28 @@
       </c>
     </row>
     <row r="35" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A35" s="171" t="s">
+      <c r="A35" s="158" t="s">
         <v>356</v>
       </c>
-      <c r="B35" s="172" t="s">
+      <c r="B35" s="159" t="s">
         <v>357</v>
       </c>
-      <c r="C35" s="172" t="s">
+      <c r="C35" s="159" t="s">
         <v>358</v>
       </c>
-      <c r="D35" s="173">
+      <c r="D35" s="160">
         <v>37048</v>
       </c>
-      <c r="E35" s="174" t="s">
+      <c r="E35" s="161" t="s">
         <v>429</v>
       </c>
-      <c r="F35" s="172">
+      <c r="F35" s="159">
         <v>1001001013</v>
       </c>
-      <c r="G35" s="175" t="s">
+      <c r="G35" s="162" t="s">
         <v>430</v>
       </c>
-      <c r="H35" s="172" t="s">
+      <c r="H35" s="159" t="s">
         <v>512</v>
       </c>
       <c r="J35" s="103" t="s">
@@ -38697,28 +38699,28 @@
       </c>
     </row>
     <row r="36" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A36" s="171" t="s">
+      <c r="A36" s="158" t="s">
         <v>356</v>
       </c>
-      <c r="B36" s="172" t="s">
+      <c r="B36" s="159" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="172" t="s">
+      <c r="C36" s="159" t="s">
         <v>358</v>
       </c>
-      <c r="D36" s="173">
+      <c r="D36" s="160">
         <v>37048</v>
       </c>
-      <c r="E36" s="174" t="s">
+      <c r="E36" s="161" t="s">
         <v>429</v>
       </c>
-      <c r="F36" s="172">
+      <c r="F36" s="159">
         <v>1001001013</v>
       </c>
-      <c r="G36" s="175" t="s">
+      <c r="G36" s="162" t="s">
         <v>430</v>
       </c>
-      <c r="H36" s="172" t="s">
+      <c r="H36" s="159" t="s">
         <v>518</v>
       </c>
       <c r="J36" s="103" t="s">
@@ -38765,28 +38767,28 @@
       </c>
     </row>
     <row r="37" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A37" s="171" t="s">
+      <c r="A37" s="158" t="s">
         <v>367</v>
       </c>
-      <c r="B37" s="172" t="s">
+      <c r="B37" s="159" t="s">
         <v>368</v>
       </c>
-      <c r="C37" s="172" t="s">
+      <c r="C37" s="159" t="s">
         <v>369</v>
       </c>
-      <c r="D37" s="173">
+      <c r="D37" s="160">
         <v>39650</v>
       </c>
-      <c r="E37" s="174" t="s">
+      <c r="E37" s="161" t="s">
         <v>429</v>
       </c>
-      <c r="F37" s="172">
+      <c r="F37" s="159">
         <v>1001001014</v>
       </c>
-      <c r="G37" s="175" t="s">
+      <c r="G37" s="162" t="s">
         <v>476</v>
       </c>
-      <c r="H37" s="172" t="s">
+      <c r="H37" s="159" t="s">
         <v>518</v>
       </c>
       <c r="J37" s="103" t="s">
@@ -38833,28 +38835,28 @@
       </c>
     </row>
     <row r="38" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A38" s="171" t="s">
+      <c r="A38" s="158" t="s">
         <v>367</v>
       </c>
-      <c r="B38" s="172" t="s">
+      <c r="B38" s="159" t="s">
         <v>368</v>
       </c>
-      <c r="C38" s="172" t="s">
+      <c r="C38" s="159" t="s">
         <v>369</v>
       </c>
-      <c r="D38" s="173">
+      <c r="D38" s="160">
         <v>39650</v>
       </c>
-      <c r="E38" s="174" t="s">
+      <c r="E38" s="161" t="s">
         <v>429</v>
       </c>
-      <c r="F38" s="172">
+      <c r="F38" s="159">
         <v>1001001014</v>
       </c>
-      <c r="G38" s="175" t="s">
+      <c r="G38" s="162" t="s">
         <v>476</v>
       </c>
-      <c r="H38" s="172" t="s">
+      <c r="H38" s="159" t="s">
         <v>518</v>
       </c>
       <c r="J38" s="103" t="s">
@@ -38901,28 +38903,28 @@
       </c>
     </row>
     <row r="39" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A39" s="171" t="s">
+      <c r="A39" s="158" t="s">
         <v>373</v>
       </c>
-      <c r="B39" s="172" t="s">
+      <c r="B39" s="159" t="s">
         <v>374</v>
       </c>
-      <c r="C39" s="172" t="s">
+      <c r="C39" s="159" t="s">
         <v>375</v>
       </c>
-      <c r="D39" s="173">
+      <c r="D39" s="160">
         <v>39784</v>
       </c>
-      <c r="E39" s="174" t="s">
+      <c r="E39" s="161" t="s">
         <v>429</v>
       </c>
-      <c r="F39" s="172">
+      <c r="F39" s="159">
         <v>1001001015</v>
       </c>
-      <c r="G39" s="175" t="s">
+      <c r="G39" s="162" t="s">
         <v>481</v>
       </c>
-      <c r="H39" s="172" t="s">
+      <c r="H39" s="159" t="s">
         <v>507</v>
       </c>
       <c r="J39" s="103" t="s">
@@ -38960,28 +38962,28 @@
       </c>
     </row>
     <row r="40" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A40" s="171" t="s">
+      <c r="A40" s="158" t="s">
         <v>373</v>
       </c>
-      <c r="B40" s="172" t="s">
+      <c r="B40" s="159" t="s">
         <v>374</v>
       </c>
-      <c r="C40" s="172" t="s">
+      <c r="C40" s="159" t="s">
         <v>375</v>
       </c>
-      <c r="D40" s="173">
+      <c r="D40" s="160">
         <v>39784</v>
       </c>
-      <c r="E40" s="174" t="s">
+      <c r="E40" s="161" t="s">
         <v>429</v>
       </c>
-      <c r="F40" s="172">
+      <c r="F40" s="159">
         <v>1001001015</v>
       </c>
-      <c r="G40" s="175" t="s">
+      <c r="G40" s="162" t="s">
         <v>481</v>
       </c>
-      <c r="H40" s="172" t="s">
+      <c r="H40" s="159" t="s">
         <v>512</v>
       </c>
       <c r="J40" s="103" t="s">
@@ -39002,10 +39004,10 @@
       <c r="P40" s="101" t="s">
         <v>373</v>
       </c>
-      <c r="R40" s="157" t="s">
+      <c r="R40" s="195" t="s">
         <v>419</v>
       </c>
-      <c r="S40" s="157"/>
+      <c r="S40" s="195"/>
       <c r="V40" s="140" t="s">
         <v>655</v>
       </c>
@@ -39023,28 +39025,28 @@
       </c>
     </row>
     <row r="41" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A41" s="171" t="s">
+      <c r="A41" s="158" t="s">
         <v>373</v>
       </c>
-      <c r="B41" s="172" t="s">
+      <c r="B41" s="159" t="s">
         <v>374</v>
       </c>
-      <c r="C41" s="172" t="s">
+      <c r="C41" s="159" t="s">
         <v>375</v>
       </c>
-      <c r="D41" s="173">
+      <c r="D41" s="160">
         <v>39784</v>
       </c>
-      <c r="E41" s="174" t="s">
+      <c r="E41" s="161" t="s">
         <v>429</v>
       </c>
-      <c r="F41" s="172">
+      <c r="F41" s="159">
         <v>1001001015</v>
       </c>
-      <c r="G41" s="175" t="s">
+      <c r="G41" s="162" t="s">
         <v>481</v>
       </c>
-      <c r="H41" s="172" t="s">
+      <c r="H41" s="159" t="s">
         <v>501</v>
       </c>
       <c r="J41" s="103" t="s">
@@ -39088,28 +39090,28 @@
       </c>
     </row>
     <row r="42" spans="1:26" ht="13.5" customHeight="1">
-      <c r="A42" s="171" t="s">
+      <c r="A42" s="158" t="s">
         <v>380</v>
       </c>
-      <c r="B42" s="172" t="s">
+      <c r="B42" s="159" t="s">
         <v>381</v>
       </c>
-      <c r="C42" s="172" t="s">
+      <c r="C42" s="159" t="s">
         <v>303</v>
       </c>
-      <c r="D42" s="173">
+      <c r="D42" s="160">
         <v>39159</v>
       </c>
-      <c r="E42" s="174" t="s">
+      <c r="E42" s="161" t="s">
         <v>420</v>
       </c>
-      <c r="F42" s="172">
+      <c r="F42" s="159">
         <v>1001001016</v>
       </c>
-      <c r="G42" s="175" t="s">
+      <c r="G42" s="162" t="s">
         <v>430</v>
       </c>
-      <c r="H42" s="172" t="s">
+      <c r="H42" s="159" t="s">
         <v>501</v>
       </c>
       <c r="J42" s="103" t="s">
@@ -39153,28 +39155,28 @@
       </c>
     </row>
     <row r="43" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A43" s="171" t="s">
+      <c r="A43" s="158" t="s">
         <v>380</v>
       </c>
-      <c r="B43" s="172" t="s">
+      <c r="B43" s="159" t="s">
         <v>381</v>
       </c>
-      <c r="C43" s="172" t="s">
+      <c r="C43" s="159" t="s">
         <v>303</v>
       </c>
-      <c r="D43" s="173">
+      <c r="D43" s="160">
         <v>39159</v>
       </c>
-      <c r="E43" s="174" t="s">
+      <c r="E43" s="161" t="s">
         <v>420</v>
       </c>
-      <c r="F43" s="172">
+      <c r="F43" s="159">
         <v>1001001016</v>
       </c>
-      <c r="G43" s="175" t="s">
+      <c r="G43" s="162" t="s">
         <v>430</v>
       </c>
-      <c r="H43" s="172" t="s">
+      <c r="H43" s="159" t="s">
         <v>501</v>
       </c>
       <c r="J43" s="103" t="s">
@@ -39218,28 +39220,28 @@
       </c>
     </row>
     <row r="44" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A44" s="171" t="s">
+      <c r="A44" s="158" t="s">
         <v>388</v>
       </c>
-      <c r="B44" s="172" t="s">
+      <c r="B44" s="159" t="s">
         <v>389</v>
       </c>
-      <c r="C44" s="172" t="s">
+      <c r="C44" s="159" t="s">
         <v>390</v>
       </c>
-      <c r="D44" s="173">
+      <c r="D44" s="160">
         <v>39720</v>
       </c>
-      <c r="E44" s="174" t="s">
+      <c r="E44" s="161" t="s">
         <v>429</v>
       </c>
-      <c r="F44" s="172">
+      <c r="F44" s="159">
         <v>1001001017</v>
       </c>
-      <c r="G44" s="175" t="s">
+      <c r="G44" s="162" t="s">
         <v>466</v>
       </c>
-      <c r="H44" s="172" t="s">
+      <c r="H44" s="159" t="s">
         <v>518</v>
       </c>
       <c r="N44" s="110" t="s">
@@ -39274,35 +39276,35 @@
       </c>
     </row>
     <row r="45" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A45" s="171" t="s">
+      <c r="A45" s="158" t="s">
         <v>388</v>
       </c>
-      <c r="B45" s="172" t="s">
+      <c r="B45" s="159" t="s">
         <v>389</v>
       </c>
-      <c r="C45" s="172" t="s">
+      <c r="C45" s="159" t="s">
         <v>390</v>
       </c>
-      <c r="D45" s="173">
+      <c r="D45" s="160">
         <v>39720</v>
       </c>
-      <c r="E45" s="174" t="s">
+      <c r="E45" s="161" t="s">
         <v>429</v>
       </c>
-      <c r="F45" s="172">
+      <c r="F45" s="159">
         <v>1001001017</v>
       </c>
-      <c r="G45" s="175" t="s">
+      <c r="G45" s="162" t="s">
         <v>466</v>
       </c>
-      <c r="H45" s="172" t="s">
+      <c r="H45" s="159" t="s">
         <v>507</v>
       </c>
-      <c r="J45" s="162" t="s">
+      <c r="J45" s="196" t="s">
         <v>534</v>
       </c>
-      <c r="K45" s="176"/>
-      <c r="L45" s="177"/>
+      <c r="K45" s="197"/>
+      <c r="L45" s="198"/>
       <c r="R45" s="105" t="s">
         <v>452</v>
       </c>
@@ -39326,28 +39328,28 @@
       </c>
     </row>
     <row r="46" spans="1:26" ht="16.5" customHeight="1">
-      <c r="A46" s="171" t="s">
+      <c r="A46" s="158" t="s">
         <v>388</v>
       </c>
-      <c r="B46" s="172" t="s">
+      <c r="B46" s="159" t="s">
         <v>389</v>
       </c>
-      <c r="C46" s="172" t="s">
+      <c r="C46" s="159" t="s">
         <v>390</v>
       </c>
-      <c r="D46" s="173">
+      <c r="D46" s="160">
         <v>39720</v>
       </c>
-      <c r="E46" s="174" t="s">
+      <c r="E46" s="161" t="s">
         <v>429</v>
       </c>
-      <c r="F46" s="172">
+      <c r="F46" s="159">
         <v>1001001017</v>
       </c>
-      <c r="G46" s="175" t="s">
+      <c r="G46" s="162" t="s">
         <v>466</v>
       </c>
-      <c r="H46" s="172" t="s">
+      <c r="H46" s="159" t="s">
         <v>518</v>
       </c>
       <c r="J46" s="113" t="s">
@@ -39359,10 +39361,10 @@
       <c r="L46" s="115" t="s">
         <v>541</v>
       </c>
-      <c r="N46" s="163" t="s">
+      <c r="N46" s="209" t="s">
         <v>408</v>
       </c>
-      <c r="O46" s="156"/>
+      <c r="O46" s="210"/>
       <c r="R46" s="105" t="s">
         <v>459</v>
       </c>
@@ -39386,28 +39388,28 @@
       </c>
     </row>
     <row r="47" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A47" s="171" t="s">
+      <c r="A47" s="158" t="s">
         <v>396</v>
       </c>
-      <c r="B47" s="172" t="s">
+      <c r="B47" s="159" t="s">
         <v>397</v>
       </c>
-      <c r="C47" s="172" t="s">
+      <c r="C47" s="159" t="s">
         <v>398</v>
       </c>
-      <c r="D47" s="173">
+      <c r="D47" s="160">
         <v>39209</v>
       </c>
-      <c r="E47" s="174" t="s">
+      <c r="E47" s="161" t="s">
         <v>429</v>
       </c>
-      <c r="F47" s="172">
+      <c r="F47" s="159">
         <v>1001001018</v>
       </c>
-      <c r="G47" s="175" t="s">
+      <c r="G47" s="162" t="s">
         <v>448</v>
       </c>
-      <c r="H47" s="172" t="s">
+      <c r="H47" s="159" t="s">
         <v>512</v>
       </c>
       <c r="J47" s="101" t="s">
@@ -39448,28 +39450,28 @@
       </c>
     </row>
     <row r="48" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A48" s="171" t="s">
+      <c r="A48" s="158" t="s">
         <v>396</v>
       </c>
-      <c r="B48" s="172" t="s">
+      <c r="B48" s="159" t="s">
         <v>397</v>
       </c>
-      <c r="C48" s="172" t="s">
+      <c r="C48" s="159" t="s">
         <v>398</v>
       </c>
-      <c r="D48" s="173">
+      <c r="D48" s="160">
         <v>39209</v>
       </c>
-      <c r="E48" s="174" t="s">
+      <c r="E48" s="161" t="s">
         <v>429</v>
       </c>
-      <c r="F48" s="172">
+      <c r="F48" s="159">
         <v>1001001018</v>
       </c>
-      <c r="G48" s="175" t="s">
+      <c r="G48" s="162" t="s">
         <v>448</v>
       </c>
-      <c r="H48" s="172" t="s">
+      <c r="H48" s="159" t="s">
         <v>512</v>
       </c>
       <c r="J48" s="101" t="s">
@@ -39510,28 +39512,28 @@
       </c>
     </row>
     <row r="49" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A49" s="171" t="s">
+      <c r="A49" s="158" t="s">
         <v>298</v>
       </c>
-      <c r="B49" s="172" t="s">
+      <c r="B49" s="159" t="s">
         <v>236</v>
       </c>
-      <c r="C49" s="172" t="s">
+      <c r="C49" s="159" t="s">
         <v>402</v>
       </c>
-      <c r="D49" s="173">
+      <c r="D49" s="160">
         <v>39765</v>
       </c>
-      <c r="E49" s="174" t="s">
+      <c r="E49" s="161" t="s">
         <v>415</v>
       </c>
-      <c r="F49" s="172">
+      <c r="F49" s="159">
         <v>1001001019</v>
       </c>
-      <c r="G49" s="175" t="s">
+      <c r="G49" s="162" t="s">
         <v>430</v>
       </c>
-      <c r="H49" s="172" t="s">
+      <c r="H49" s="159" t="s">
         <v>512</v>
       </c>
       <c r="J49" s="101" t="s">
@@ -39572,28 +39574,28 @@
       </c>
     </row>
     <row r="50" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A50" s="171" t="s">
+      <c r="A50" s="158" t="s">
         <v>298</v>
       </c>
-      <c r="B50" s="172" t="s">
+      <c r="B50" s="159" t="s">
         <v>236</v>
       </c>
-      <c r="C50" s="172" t="s">
+      <c r="C50" s="159" t="s">
         <v>402</v>
       </c>
-      <c r="D50" s="173">
+      <c r="D50" s="160">
         <v>39765</v>
       </c>
-      <c r="E50" s="174" t="s">
+      <c r="E50" s="161" t="s">
         <v>415</v>
       </c>
-      <c r="F50" s="172">
+      <c r="F50" s="159">
         <v>1001001019</v>
       </c>
-      <c r="G50" s="175" t="s">
+      <c r="G50" s="162" t="s">
         <v>430</v>
       </c>
-      <c r="H50" s="172" t="s">
+      <c r="H50" s="159" t="s">
         <v>501</v>
       </c>
       <c r="J50" s="101" t="s">
@@ -39634,28 +39636,28 @@
       </c>
     </row>
     <row r="51" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A51" s="171" t="s">
+      <c r="A51" s="158" t="s">
         <v>298</v>
       </c>
-      <c r="B51" s="172" t="s">
+      <c r="B51" s="159" t="s">
         <v>236</v>
       </c>
-      <c r="C51" s="172" t="s">
+      <c r="C51" s="159" t="s">
         <v>402</v>
       </c>
-      <c r="D51" s="173">
+      <c r="D51" s="160">
         <v>39765</v>
       </c>
-      <c r="E51" s="174" t="s">
+      <c r="E51" s="161" t="s">
         <v>415</v>
       </c>
-      <c r="F51" s="172">
+      <c r="F51" s="159">
         <v>1001001019</v>
       </c>
-      <c r="G51" s="175" t="s">
+      <c r="G51" s="162" t="s">
         <v>430</v>
       </c>
-      <c r="H51" s="172" t="s">
+      <c r="H51" s="159" t="s">
         <v>512</v>
       </c>
       <c r="J51" s="101" t="s">
@@ -41094,73 +41096,73 @@
     <row r="999" ht="15.75" customHeight="1"/>
   </sheetData>
   <customSheetViews>
+    <customSheetView guid="{4BE0AE49-5167-486F-A74B-07AF5BFCAA2A}" filter="1" showAutoFilter="1">
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <autoFilter ref="E80:G99" xr:uid="{F65CFEB8-6B68-4109-84A2-4441358A7D71}"/>
+      <extLst>
+        <ext uri="GoogleSheetsCustomDataVersion1">
+          <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="769624659"/>
+        </ext>
+      </extLst>
+    </customSheetView>
+    <customSheetView guid="{D65A4ACE-247C-439E-AEA8-2EA75470FCA5}" filter="1" showAutoFilter="1">
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <autoFilter ref="K53:L57" xr:uid="{4C770E63-15AE-4B57-A2E5-C85EEC4052FC}"/>
+      <extLst>
+        <ext uri="GoogleSheetsCustomDataVersion1">
+          <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="60796271"/>
+        </ext>
+      </extLst>
+    </customSheetView>
+    <customSheetView guid="{626D8D2F-B7BD-49F0-B146-21AFFE642FF9}" filter="1" showAutoFilter="1">
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <autoFilter ref="B80:C92" xr:uid="{060121E8-5ABA-4D0C-98A0-68A24F7D3D63}"/>
+      <extLst>
+        <ext uri="GoogleSheetsCustomDataVersion1">
+          <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="22588955"/>
+        </ext>
+      </extLst>
+    </customSheetView>
+    <customSheetView guid="{5BA99981-AF65-4323-B2F8-5F691FA1504F}" filter="1" showAutoFilter="1">
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <autoFilter ref="U55:Y104" xr:uid="{95D44E9C-61E6-4373-A1B7-2C59A995F4F6}"/>
+      <extLst>
+        <ext uri="GoogleSheetsCustomDataVersion1">
+          <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="2069367905"/>
+        </ext>
+      </extLst>
+    </customSheetView>
+    <customSheetView guid="{7812FD8C-0E59-45E2-87A2-7698E6BE27A1}" filter="1" showAutoFilter="1">
+      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+      <autoFilter ref="A53:G72" xr:uid="{EE4BBFC3-B95A-4D4F-B33E-E0AE8E4BADA0}"/>
+      <extLst>
+        <ext uri="GoogleSheetsCustomDataVersion1">
+          <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="1795137491"/>
+        </ext>
+      </extLst>
+    </customSheetView>
     <customSheetView guid="{E35139AA-24E9-4A62-81CA-588D087135E4}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="I80:K99" xr:uid="{6E466FD5-D61E-4B0F-87FB-34F280A4A9C9}"/>
+      <autoFilter ref="I80:K99" xr:uid="{2EC12B49-6739-4805-BF7B-9315666020B6}"/>
       <extLst>
         <ext uri="GoogleSheetsCustomDataVersion1">
           <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="1238617615"/>
         </ext>
       </extLst>
     </customSheetView>
-    <customSheetView guid="{7812FD8C-0E59-45E2-87A2-7698E6BE27A1}" filter="1" showAutoFilter="1">
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A53:G72" xr:uid="{E19E7C68-BE48-4189-8643-C5CF8D341853}"/>
-      <extLst>
-        <ext uri="GoogleSheetsCustomDataVersion1">
-          <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="1795137491"/>
-        </ext>
-      </extLst>
-    </customSheetView>
-    <customSheetView guid="{5BA99981-AF65-4323-B2F8-5F691FA1504F}" filter="1" showAutoFilter="1">
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="U55:Y104" xr:uid="{B893FA35-6743-4B41-94B5-158D65F0E2DB}"/>
-      <extLst>
-        <ext uri="GoogleSheetsCustomDataVersion1">
-          <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="2069367905"/>
-        </ext>
-      </extLst>
-    </customSheetView>
-    <customSheetView guid="{626D8D2F-B7BD-49F0-B146-21AFFE642FF9}" filter="1" showAutoFilter="1">
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="B80:C92" xr:uid="{B816A348-C24A-4EB1-98CC-0CDB5FB08FE0}"/>
-      <extLst>
-        <ext uri="GoogleSheetsCustomDataVersion1">
-          <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="22588955"/>
-        </ext>
-      </extLst>
-    </customSheetView>
-    <customSheetView guid="{D65A4ACE-247C-439E-AEA8-2EA75470FCA5}" filter="1" showAutoFilter="1">
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="K53:L57" xr:uid="{12A3B3B8-8A4B-4416-B4A1-07BED02DC590}"/>
-      <extLst>
-        <ext uri="GoogleSheetsCustomDataVersion1">
-          <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="60796271"/>
-        </ext>
-      </extLst>
-    </customSheetView>
-    <customSheetView guid="{4BE0AE49-5167-486F-A74B-07AF5BFCAA2A}" filter="1" showAutoFilter="1">
-      <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="E80:G99" xr:uid="{B5C949D8-457A-48E7-BE89-44A4F7856280}"/>
-      <extLst>
-        <ext uri="GoogleSheetsCustomDataVersion1">
-          <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="769624659"/>
-        </ext>
-      </extLst>
-    </customSheetView>
   </customSheetViews>
   <mergeCells count="11">
+    <mergeCell ref="N46:O46"/>
+    <mergeCell ref="J45:L45"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="J16:L16"/>
     <mergeCell ref="V1:Z1"/>
     <mergeCell ref="N24:P24"/>
     <mergeCell ref="N1:P1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="R40:S40"/>
-    <mergeCell ref="J45:L45"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="N46:O46"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -41202,46 +41204,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="15" customHeight="1">
-      <c r="A1" s="168" t="s">
+      <c r="A1" s="212" t="s">
         <v>688</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="166"/>
-      <c r="F1" s="162" t="s">
+      <c r="B1" s="212"/>
+      <c r="C1" s="212"/>
+      <c r="D1" s="212"/>
+      <c r="E1" s="154"/>
+      <c r="F1" s="196" t="s">
         <v>534</v>
       </c>
-      <c r="G1" s="176"/>
-      <c r="H1" s="166"/>
-      <c r="J1" s="202" t="s">
+      <c r="G1" s="197"/>
+      <c r="H1" s="154"/>
+      <c r="J1" s="213" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="213"/>
-      <c r="N1" s="161" t="s">
+      <c r="K1" s="214"/>
+      <c r="N1" s="191" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="182"/>
-      <c r="P1" s="191"/>
-      <c r="R1" s="153" t="s">
+      <c r="O1" s="192"/>
+      <c r="P1" s="169"/>
+      <c r="R1" s="202" t="s">
         <v>9</v>
       </c>
-      <c r="S1" s="154"/>
-      <c r="T1" s="209"/>
-      <c r="U1" s="157" t="s">
+      <c r="S1" s="203"/>
+      <c r="T1" s="185"/>
+      <c r="U1" s="195" t="s">
         <v>419</v>
       </c>
-      <c r="V1" s="157"/>
-      <c r="Z1" s="165"/>
+      <c r="V1" s="195"/>
+      <c r="Z1" s="153"/>
     </row>
     <row r="2" spans="1:26">
-      <c r="A2" s="192" t="s">
+      <c r="A2" s="170" t="s">
         <v>409</v>
       </c>
-      <c r="B2" s="194" t="s">
+      <c r="B2" s="172" t="s">
         <v>411</v>
       </c>
-      <c r="C2" s="170" t="s">
+      <c r="C2" s="157" t="s">
         <v>412</v>
       </c>
       <c r="D2" s="152" t="s">
@@ -41256,13 +41258,13 @@
       <c r="J2" s="111" t="s">
         <v>551</v>
       </c>
-      <c r="K2" s="186" t="s">
+      <c r="K2" s="164" t="s">
         <v>549</v>
       </c>
-      <c r="N2" s="186" t="s">
+      <c r="N2" s="164" t="s">
         <v>549</v>
       </c>
-      <c r="O2" s="203" t="s">
+      <c r="O2" s="180" t="s">
         <v>493</v>
       </c>
       <c r="R2" s="126" t="s">
@@ -41271,7 +41273,7 @@
       <c r="S2" s="127" t="s">
         <v>494</v>
       </c>
-      <c r="T2" s="211"/>
+      <c r="T2" s="186"/>
       <c r="U2" s="150" t="s">
         <v>427</v>
       </c>
@@ -41280,16 +41282,16 @@
       </c>
     </row>
     <row r="3" spans="1:26">
-      <c r="A3" s="193" t="s">
+      <c r="A3" s="171" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="195" t="s">
+      <c r="B3" s="173" t="s">
         <v>415</v>
       </c>
-      <c r="C3" s="175" t="s">
+      <c r="C3" s="162" t="s">
         <v>416</v>
       </c>
-      <c r="D3" s="172" t="s">
+      <c r="D3" s="159" t="s">
         <v>501</v>
       </c>
       <c r="F3" s="101" t="s">
@@ -41310,14 +41312,14 @@
       <c r="O3" s="102" t="s">
         <v>501</v>
       </c>
-      <c r="P3" s="189"/>
+      <c r="P3" s="167"/>
       <c r="R3" s="128" t="s">
         <v>501</v>
       </c>
       <c r="S3" s="129" t="s">
         <v>27</v>
       </c>
-      <c r="T3" s="167"/>
+      <c r="T3" s="155"/>
       <c r="U3" s="119" t="s">
         <v>435</v>
       </c>
@@ -41326,16 +41328,16 @@
       </c>
     </row>
     <row r="4" spans="1:26">
-      <c r="A4" s="193" t="s">
+      <c r="A4" s="171" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="195" t="s">
+      <c r="B4" s="173" t="s">
         <v>415</v>
       </c>
-      <c r="C4" s="175" t="s">
+      <c r="C4" s="162" t="s">
         <v>416</v>
       </c>
-      <c r="D4" s="172" t="s">
+      <c r="D4" s="159" t="s">
         <v>512</v>
       </c>
       <c r="F4" s="101" t="s">
@@ -41356,14 +41358,14 @@
       <c r="O4" s="102" t="s">
         <v>501</v>
       </c>
-      <c r="P4" s="189"/>
+      <c r="P4" s="167"/>
       <c r="R4" s="130" t="s">
         <v>507</v>
       </c>
       <c r="S4" s="131" t="s">
         <v>92</v>
       </c>
-      <c r="T4" s="208"/>
+      <c r="T4" s="184"/>
       <c r="U4" s="105" t="s">
         <v>441</v>
       </c>
@@ -41372,16 +41374,16 @@
       </c>
     </row>
     <row r="5" spans="1:26">
-      <c r="A5" s="193" t="s">
+      <c r="A5" s="171" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="195" t="s">
+      <c r="B5" s="173" t="s">
         <v>415</v>
       </c>
-      <c r="C5" s="175" t="s">
+      <c r="C5" s="162" t="s">
         <v>416</v>
       </c>
-      <c r="D5" s="172" t="s">
+      <c r="D5" s="159" t="s">
         <v>518</v>
       </c>
       <c r="F5" s="101" t="s">
@@ -41402,14 +41404,14 @@
       <c r="O5" s="102" t="s">
         <v>501</v>
       </c>
-      <c r="P5" s="189"/>
+      <c r="P5" s="167"/>
       <c r="R5" s="128" t="s">
         <v>512</v>
       </c>
       <c r="S5" s="129" t="s">
         <v>40</v>
       </c>
-      <c r="T5" s="208"/>
+      <c r="T5" s="184"/>
       <c r="U5" s="105" t="s">
         <v>447</v>
       </c>
@@ -41418,16 +41420,16 @@
       </c>
     </row>
     <row r="6" spans="1:26">
-      <c r="A6" s="193" t="s">
+      <c r="A6" s="171" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="195" t="s">
+      <c r="B6" s="173" t="s">
         <v>420</v>
       </c>
-      <c r="C6" s="175" t="s">
+      <c r="C6" s="162" t="s">
         <v>421</v>
       </c>
-      <c r="D6" s="172" t="s">
+      <c r="D6" s="159" t="s">
         <v>518</v>
       </c>
       <c r="F6" s="101" t="s">
@@ -41448,14 +41450,14 @@
       <c r="O6" s="102" t="s">
         <v>501</v>
       </c>
-      <c r="P6" s="189"/>
+      <c r="P6" s="167"/>
       <c r="R6" s="132" t="s">
         <v>518</v>
       </c>
       <c r="S6" s="133" t="s">
         <v>53</v>
       </c>
-      <c r="T6" s="208"/>
+      <c r="T6" s="184"/>
       <c r="U6" s="105" t="s">
         <v>452</v>
       </c>
@@ -41464,16 +41466,16 @@
       </c>
     </row>
     <row r="7" spans="1:26">
-      <c r="A7" s="193" t="s">
+      <c r="A7" s="171" t="s">
         <v>62</v>
       </c>
-      <c r="B7" s="195" t="s">
+      <c r="B7" s="173" t="s">
         <v>420</v>
       </c>
-      <c r="C7" s="175" t="s">
+      <c r="C7" s="162" t="s">
         <v>421</v>
       </c>
-      <c r="D7" s="172" t="s">
+      <c r="D7" s="159" t="s">
         <v>507</v>
       </c>
       <c r="F7" s="101" t="s">
@@ -41488,14 +41490,14 @@
       <c r="K7" s="116" t="s">
         <v>577</v>
       </c>
-      <c r="N7" s="187" t="s">
+      <c r="N7" s="165" t="s">
         <v>577</v>
       </c>
-      <c r="O7" s="188" t="s">
+      <c r="O7" s="166" t="s">
         <v>501</v>
       </c>
-      <c r="P7" s="189"/>
-      <c r="T7" s="208"/>
+      <c r="P7" s="167"/>
+      <c r="T7" s="184"/>
       <c r="U7" s="105" t="s">
         <v>459</v>
       </c>
@@ -41504,16 +41506,16 @@
       </c>
     </row>
     <row r="8" spans="1:26">
-      <c r="A8" s="193" t="s">
+      <c r="A8" s="171" t="s">
         <v>98</v>
       </c>
-      <c r="B8" s="195" t="s">
+      <c r="B8" s="173" t="s">
         <v>429</v>
       </c>
-      <c r="C8" s="175" t="s">
+      <c r="C8" s="162" t="s">
         <v>430</v>
       </c>
-      <c r="D8" s="172" t="s">
+      <c r="D8" s="159" t="s">
         <v>512</v>
       </c>
       <c r="F8" s="101" t="s">
@@ -41534,12 +41536,12 @@
       <c r="O8" s="102" t="s">
         <v>501</v>
       </c>
-      <c r="P8" s="189"/>
-      <c r="R8" s="164" t="s">
+      <c r="P8" s="167"/>
+      <c r="R8" s="204" t="s">
         <v>492</v>
       </c>
-      <c r="S8" s="181"/>
-      <c r="T8" s="208"/>
+      <c r="S8" s="205"/>
+      <c r="T8" s="184"/>
       <c r="U8" s="105" t="s">
         <v>465</v>
       </c>
@@ -41548,16 +41550,16 @@
       </c>
     </row>
     <row r="9" spans="1:26">
-      <c r="A9" s="193" t="s">
+      <c r="A9" s="171" t="s">
         <v>98</v>
       </c>
-      <c r="B9" s="195" t="s">
+      <c r="B9" s="173" t="s">
         <v>429</v>
       </c>
-      <c r="C9" s="175" t="s">
+      <c r="C9" s="162" t="s">
         <v>430</v>
       </c>
-      <c r="D9" s="172" t="s">
+      <c r="D9" s="159" t="s">
         <v>501</v>
       </c>
       <c r="F9" s="101" t="s">
@@ -41578,14 +41580,14 @@
       <c r="O9" s="102" t="s">
         <v>507</v>
       </c>
-      <c r="P9" s="189"/>
+      <c r="P9" s="167"/>
       <c r="R9" s="112" t="s">
         <v>499</v>
       </c>
       <c r="S9" s="111" t="s">
         <v>500</v>
       </c>
-      <c r="T9" s="208"/>
+      <c r="T9" s="184"/>
       <c r="U9" s="105" t="s">
         <v>470</v>
       </c>
@@ -41594,16 +41596,16 @@
       </c>
     </row>
     <row r="10" spans="1:26">
-      <c r="A10" s="193" t="s">
+      <c r="A10" s="171" t="s">
         <v>98</v>
       </c>
-      <c r="B10" s="195" t="s">
+      <c r="B10" s="173" t="s">
         <v>429</v>
       </c>
-      <c r="C10" s="175" t="s">
+      <c r="C10" s="162" t="s">
         <v>430</v>
       </c>
-      <c r="D10" s="172" t="s">
+      <c r="D10" s="159" t="s">
         <v>507</v>
       </c>
       <c r="F10" s="101" t="s">
@@ -41624,14 +41626,14 @@
       <c r="O10" s="102" t="s">
         <v>507</v>
       </c>
-      <c r="P10" s="189"/>
+      <c r="P10" s="167"/>
       <c r="R10" s="3" t="s">
         <v>415</v>
       </c>
       <c r="S10" s="103" t="s">
         <v>24</v>
       </c>
-      <c r="T10" s="208"/>
+      <c r="T10" s="184"/>
       <c r="U10" s="105" t="s">
         <v>475</v>
       </c>
@@ -41640,16 +41642,16 @@
       </c>
     </row>
     <row r="11" spans="1:26">
-      <c r="A11" s="193" t="s">
+      <c r="A11" s="171" t="s">
         <v>165</v>
       </c>
-      <c r="B11" s="195" t="s">
+      <c r="B11" s="173" t="s">
         <v>415</v>
       </c>
-      <c r="C11" s="175" t="s">
+      <c r="C11" s="162" t="s">
         <v>436</v>
       </c>
-      <c r="D11" s="172" t="s">
+      <c r="D11" s="159" t="s">
         <v>501</v>
       </c>
       <c r="F11" s="101" t="s">
@@ -41670,14 +41672,14 @@
       <c r="O11" s="102" t="s">
         <v>507</v>
       </c>
-      <c r="P11" s="189"/>
+      <c r="P11" s="167"/>
       <c r="R11" s="3" t="s">
         <v>429</v>
       </c>
       <c r="S11" s="103" t="s">
         <v>113</v>
       </c>
-      <c r="T11" s="208"/>
+      <c r="T11" s="184"/>
       <c r="U11" s="105" t="s">
         <v>480</v>
       </c>
@@ -41686,16 +41688,16 @@
       </c>
     </row>
     <row r="12" spans="1:26">
-      <c r="A12" s="193" t="s">
+      <c r="A12" s="171" t="s">
         <v>165</v>
       </c>
-      <c r="B12" s="195" t="s">
+      <c r="B12" s="173" t="s">
         <v>415</v>
       </c>
-      <c r="C12" s="175" t="s">
+      <c r="C12" s="162" t="s">
         <v>436</v>
       </c>
-      <c r="D12" s="172" t="s">
+      <c r="D12" s="159" t="s">
         <v>512</v>
       </c>
       <c r="F12" s="101" t="s">
@@ -41716,14 +41718,14 @@
       <c r="O12" s="102" t="s">
         <v>507</v>
       </c>
-      <c r="P12" s="189"/>
+      <c r="P12" s="167"/>
       <c r="R12" s="3" t="s">
         <v>420</v>
       </c>
       <c r="S12" s="103" t="s">
         <v>517</v>
       </c>
-      <c r="T12" s="208"/>
+      <c r="T12" s="184"/>
       <c r="U12" s="105" t="s">
         <v>486</v>
       </c>
@@ -41732,16 +41734,16 @@
       </c>
     </row>
     <row r="13" spans="1:26">
-      <c r="A13" s="193" t="s">
+      <c r="A13" s="171" t="s">
         <v>197</v>
       </c>
-      <c r="B13" s="195" t="s">
+      <c r="B13" s="173" t="s">
         <v>429</v>
       </c>
-      <c r="C13" s="175" t="s">
+      <c r="C13" s="162" t="s">
         <v>442</v>
       </c>
-      <c r="D13" s="172" t="s">
+      <c r="D13" s="159" t="s">
         <v>518</v>
       </c>
       <c r="F13" s="101" t="s">
@@ -41762,14 +41764,14 @@
       <c r="O13" s="102" t="s">
         <v>507</v>
       </c>
-      <c r="P13" s="189"/>
+      <c r="P13" s="167"/>
       <c r="R13" s="3" t="s">
         <v>453</v>
       </c>
       <c r="S13" s="103" t="s">
         <v>267</v>
       </c>
-      <c r="T13" s="208"/>
+      <c r="T13" s="184"/>
       <c r="U13" s="105" t="s">
         <v>491</v>
       </c>
@@ -41778,16 +41780,16 @@
       </c>
     </row>
     <row r="14" spans="1:26">
-      <c r="A14" s="193" t="s">
+      <c r="A14" s="171" t="s">
         <v>197</v>
       </c>
-      <c r="B14" s="195" t="s">
+      <c r="B14" s="173" t="s">
         <v>429</v>
       </c>
-      <c r="C14" s="175" t="s">
+      <c r="C14" s="162" t="s">
         <v>442</v>
       </c>
-      <c r="D14" s="172" t="s">
+      <c r="D14" s="159" t="s">
         <v>518</v>
       </c>
       <c r="F14" s="101" t="s">
@@ -41808,8 +41810,8 @@
       <c r="O14" s="102" t="s">
         <v>512</v>
       </c>
-      <c r="P14" s="189"/>
-      <c r="T14" s="208"/>
+      <c r="P14" s="167"/>
+      <c r="T14" s="184"/>
       <c r="U14" s="105" t="s">
         <v>498</v>
       </c>
@@ -41818,22 +41820,22 @@
       </c>
     </row>
     <row r="15" spans="1:26">
-      <c r="A15" s="193" t="s">
+      <c r="A15" s="171" t="s">
         <v>197</v>
       </c>
-      <c r="B15" s="195" t="s">
+      <c r="B15" s="173" t="s">
         <v>429</v>
       </c>
-      <c r="C15" s="175" t="s">
+      <c r="C15" s="162" t="s">
         <v>442</v>
       </c>
-      <c r="D15" s="172" t="s">
+      <c r="D15" s="159" t="s">
         <v>507</v>
       </c>
       <c r="F15" s="101" t="s">
         <v>626</v>
       </c>
-      <c r="G15" s="196" t="s">
+      <c r="G15" s="174" t="s">
         <v>356</v>
       </c>
       <c r="J15" s="103" t="s">
@@ -41848,12 +41850,12 @@
       <c r="O15" s="102" t="s">
         <v>512</v>
       </c>
-      <c r="P15" s="189"/>
-      <c r="R15" s="163" t="s">
+      <c r="P15" s="167"/>
+      <c r="R15" s="209" t="s">
         <v>408</v>
       </c>
-      <c r="S15" s="156"/>
-      <c r="T15" s="208"/>
+      <c r="S15" s="210"/>
+      <c r="T15" s="184"/>
       <c r="U15" s="105" t="s">
         <v>506</v>
       </c>
@@ -41862,22 +41864,22 @@
       </c>
     </row>
     <row r="16" spans="1:26">
-      <c r="A16" s="193" t="s">
+      <c r="A16" s="171" t="s">
         <v>234</v>
       </c>
-      <c r="B16" s="195" t="s">
+      <c r="B16" s="173" t="s">
         <v>429</v>
       </c>
-      <c r="C16" s="175" t="s">
+      <c r="C16" s="162" t="s">
         <v>430</v>
       </c>
-      <c r="D16" s="172" t="s">
+      <c r="D16" s="159" t="s">
         <v>501</v>
       </c>
       <c r="F16" s="101" t="s">
         <v>632</v>
       </c>
-      <c r="G16" s="196" t="s">
+      <c r="G16" s="174" t="s">
         <v>367</v>
       </c>
       <c r="J16" s="103" t="s">
@@ -41886,21 +41888,21 @@
       <c r="K16" s="116" t="s">
         <v>619</v>
       </c>
-      <c r="L16" s="199"/>
+      <c r="L16" s="177"/>
       <c r="N16" s="116" t="s">
         <v>632</v>
       </c>
       <c r="O16" s="102" t="s">
         <v>512</v>
       </c>
-      <c r="P16" s="189"/>
+      <c r="P16" s="167"/>
       <c r="R16" s="120" t="s">
         <v>413</v>
       </c>
       <c r="S16" s="121" t="s">
         <v>414</v>
       </c>
-      <c r="T16" s="208"/>
+      <c r="T16" s="184"/>
       <c r="U16" s="105" t="s">
         <v>511</v>
       </c>
@@ -41909,22 +41911,22 @@
       </c>
     </row>
     <row r="17" spans="1:28">
-      <c r="A17" s="193" t="s">
+      <c r="A17" s="171" t="s">
         <v>234</v>
       </c>
-      <c r="B17" s="195" t="s">
+      <c r="B17" s="173" t="s">
         <v>429</v>
       </c>
-      <c r="C17" s="175" t="s">
+      <c r="C17" s="162" t="s">
         <v>430</v>
       </c>
-      <c r="D17" s="172" t="s">
+      <c r="D17" s="159" t="s">
         <v>501</v>
       </c>
       <c r="F17" s="101" t="s">
         <v>639</v>
       </c>
-      <c r="G17" s="196" t="s">
+      <c r="G17" s="174" t="s">
         <v>373</v>
       </c>
       <c r="J17" s="103" t="s">
@@ -41933,21 +41935,21 @@
       <c r="K17" s="116" t="s">
         <v>639</v>
       </c>
-      <c r="L17" s="200"/>
+      <c r="L17" s="178"/>
       <c r="N17" s="116" t="s">
         <v>639</v>
       </c>
       <c r="O17" s="102" t="s">
         <v>512</v>
       </c>
-      <c r="P17" s="189"/>
+      <c r="P17" s="167"/>
       <c r="R17" s="122" t="s">
         <v>416</v>
       </c>
       <c r="S17" s="123" t="s">
         <v>26</v>
       </c>
-      <c r="T17" s="208"/>
+      <c r="T17" s="184"/>
       <c r="U17" s="105" t="s">
         <v>516</v>
       </c>
@@ -41956,22 +41958,22 @@
       </c>
     </row>
     <row r="18" spans="1:28">
-      <c r="A18" s="193" t="s">
+      <c r="A18" s="171" t="s">
         <v>261</v>
       </c>
-      <c r="B18" s="195" t="s">
+      <c r="B18" s="173" t="s">
         <v>453</v>
       </c>
-      <c r="C18" s="175" t="s">
+      <c r="C18" s="162" t="s">
         <v>454</v>
       </c>
-      <c r="D18" s="172" t="s">
+      <c r="D18" s="159" t="s">
         <v>501</v>
       </c>
       <c r="F18" s="101" t="s">
         <v>644</v>
       </c>
-      <c r="G18" s="196" t="s">
+      <c r="G18" s="174" t="s">
         <v>380</v>
       </c>
       <c r="J18" s="103" t="s">
@@ -41980,21 +41982,21 @@
       <c r="K18" s="116" t="s">
         <v>626</v>
       </c>
-      <c r="L18" s="201"/>
+      <c r="L18" s="179"/>
       <c r="N18" s="116" t="s">
         <v>644</v>
       </c>
       <c r="O18" s="102" t="s">
         <v>512</v>
       </c>
-      <c r="P18" s="189"/>
+      <c r="P18" s="167"/>
       <c r="R18" s="122" t="s">
         <v>421</v>
       </c>
       <c r="S18" s="123" t="s">
         <v>47</v>
       </c>
-      <c r="T18" s="208"/>
+      <c r="T18" s="184"/>
       <c r="U18" s="105" t="s">
         <v>523</v>
       </c>
@@ -42003,22 +42005,22 @@
       </c>
     </row>
     <row r="19" spans="1:28">
-      <c r="A19" s="193" t="s">
+      <c r="A19" s="171" t="s">
         <v>261</v>
       </c>
-      <c r="B19" s="195" t="s">
+      <c r="B19" s="173" t="s">
         <v>453</v>
       </c>
-      <c r="C19" s="175" t="s">
+      <c r="C19" s="162" t="s">
         <v>454</v>
       </c>
-      <c r="D19" s="172" t="s">
+      <c r="D19" s="159" t="s">
         <v>518</v>
       </c>
       <c r="F19" s="101" t="s">
         <v>649</v>
       </c>
-      <c r="G19" s="196" t="s">
+      <c r="G19" s="174" t="s">
         <v>388</v>
       </c>
       <c r="J19" s="103" t="s">
@@ -42027,21 +42029,21 @@
       <c r="K19" s="116" t="s">
         <v>644</v>
       </c>
-      <c r="L19" s="201"/>
+      <c r="L19" s="179"/>
       <c r="N19" s="116" t="s">
         <v>649</v>
       </c>
       <c r="O19" s="102" t="s">
         <v>518</v>
       </c>
-      <c r="P19" s="189"/>
+      <c r="P19" s="167"/>
       <c r="R19" s="122" t="s">
         <v>430</v>
       </c>
       <c r="S19" s="123" t="s">
         <v>64</v>
       </c>
-      <c r="T19" s="208"/>
+      <c r="T19" s="184"/>
       <c r="U19" s="105" t="s">
         <v>528</v>
       </c>
@@ -42050,22 +42052,22 @@
       </c>
     </row>
     <row r="20" spans="1:28">
-      <c r="A20" s="193" t="s">
+      <c r="A20" s="171" t="s">
         <v>261</v>
       </c>
-      <c r="B20" s="195" t="s">
+      <c r="B20" s="173" t="s">
         <v>453</v>
       </c>
-      <c r="C20" s="175" t="s">
+      <c r="C20" s="162" t="s">
         <v>454</v>
       </c>
-      <c r="D20" s="172" t="s">
+      <c r="D20" s="159" t="s">
         <v>512</v>
       </c>
       <c r="F20" s="101" t="s">
         <v>653</v>
       </c>
-      <c r="G20" s="196" t="s">
+      <c r="G20" s="174" t="s">
         <v>396</v>
       </c>
       <c r="J20" s="103" t="s">
@@ -42074,21 +42076,21 @@
       <c r="K20" s="116" t="s">
         <v>626</v>
       </c>
-      <c r="L20" s="201"/>
+      <c r="L20" s="179"/>
       <c r="N20" s="116" t="s">
         <v>653</v>
       </c>
       <c r="O20" s="102" t="s">
         <v>518</v>
       </c>
-      <c r="P20" s="189"/>
+      <c r="P20" s="167"/>
       <c r="R20" s="122" t="s">
         <v>436</v>
       </c>
       <c r="S20" s="123" t="s">
         <v>81</v>
       </c>
-      <c r="T20" s="208"/>
+      <c r="T20" s="184"/>
       <c r="U20" s="105" t="s">
         <v>533</v>
       </c>
@@ -42097,22 +42099,22 @@
       </c>
     </row>
     <row r="21" spans="1:28">
-      <c r="A21" s="193" t="s">
+      <c r="A21" s="171" t="s">
         <v>300</v>
       </c>
-      <c r="B21" s="195" t="s">
+      <c r="B21" s="173" t="s">
         <v>453</v>
       </c>
-      <c r="C21" s="175" t="s">
+      <c r="C21" s="162" t="s">
         <v>460</v>
       </c>
-      <c r="D21" s="172" t="s">
+      <c r="D21" s="159" t="s">
         <v>507</v>
       </c>
       <c r="F21" s="108" t="s">
         <v>658</v>
       </c>
-      <c r="G21" s="197" t="s">
+      <c r="G21" s="175" t="s">
         <v>298</v>
       </c>
       <c r="J21" s="103" t="s">
@@ -42121,21 +42123,21 @@
       <c r="K21" s="116" t="s">
         <v>632</v>
       </c>
-      <c r="L21" s="201"/>
+      <c r="L21" s="179"/>
       <c r="N21" s="116" t="s">
         <v>658</v>
       </c>
       <c r="O21" s="102" t="s">
         <v>518</v>
       </c>
-      <c r="P21" s="189"/>
+      <c r="P21" s="167"/>
       <c r="R21" s="122" t="s">
         <v>442</v>
       </c>
       <c r="S21" s="123" t="s">
         <v>97</v>
       </c>
-      <c r="T21" s="208"/>
+      <c r="T21" s="184"/>
       <c r="U21" s="105" t="s">
         <v>539</v>
       </c>
@@ -42144,40 +42146,40 @@
       </c>
     </row>
     <row r="22" spans="1:28">
-      <c r="A22" s="193" t="s">
+      <c r="A22" s="171" t="s">
         <v>300</v>
       </c>
-      <c r="B22" s="195" t="s">
+      <c r="B22" s="173" t="s">
         <v>453</v>
       </c>
-      <c r="C22" s="175" t="s">
+      <c r="C22" s="162" t="s">
         <v>460</v>
       </c>
-      <c r="D22" s="172" t="s">
+      <c r="D22" s="159" t="s">
         <v>518</v>
       </c>
-      <c r="F22" s="167"/>
+      <c r="F22" s="155"/>
       <c r="J22" s="103" t="s">
         <v>668</v>
       </c>
       <c r="K22" s="116" t="s">
         <v>639</v>
       </c>
-      <c r="L22" s="201"/>
+      <c r="L22" s="179"/>
       <c r="N22" s="116" t="s">
         <v>667</v>
       </c>
       <c r="O22" s="102" t="s">
         <v>518</v>
       </c>
-      <c r="P22" s="189"/>
+      <c r="P22" s="167"/>
       <c r="R22" s="122" t="s">
         <v>448</v>
       </c>
       <c r="S22" s="123" t="s">
         <v>288</v>
       </c>
-      <c r="T22" s="208"/>
+      <c r="T22" s="184"/>
       <c r="U22" s="105" t="s">
         <v>546</v>
       </c>
@@ -42186,36 +42188,36 @@
       </c>
     </row>
     <row r="23" spans="1:28">
-      <c r="A23" s="193" t="s">
+      <c r="A23" s="171" t="s">
         <v>315</v>
       </c>
-      <c r="B23" s="195" t="s">
+      <c r="B23" s="173" t="s">
         <v>453</v>
       </c>
-      <c r="C23" s="175" t="s">
+      <c r="C23" s="162" t="s">
         <v>466</v>
       </c>
-      <c r="D23" s="172" t="s">
+      <c r="D23" s="159" t="s">
         <v>501</v>
       </c>
-      <c r="F23" s="161" t="s">
+      <c r="F23" s="191" t="s">
         <v>6</v>
       </c>
-      <c r="G23" s="182"/>
+      <c r="G23" s="192"/>
       <c r="J23" s="103" t="s">
         <v>598</v>
       </c>
       <c r="K23" s="116" t="s">
         <v>649</v>
       </c>
-      <c r="L23" s="201"/>
+      <c r="L23" s="179"/>
       <c r="R23" s="122" t="s">
         <v>454</v>
       </c>
       <c r="S23" s="123" t="s">
         <v>126</v>
       </c>
-      <c r="T23" s="208"/>
+      <c r="T23" s="184"/>
       <c r="U23" s="105" t="s">
         <v>557</v>
       </c>
@@ -42225,22 +42227,22 @@
       <c r="AB23" s="80"/>
     </row>
     <row r="24" spans="1:28">
-      <c r="A24" s="193" t="s">
+      <c r="A24" s="171" t="s">
         <v>315</v>
       </c>
-      <c r="B24" s="195" t="s">
+      <c r="B24" s="173" t="s">
         <v>453</v>
       </c>
-      <c r="C24" s="175" t="s">
+      <c r="C24" s="162" t="s">
         <v>466</v>
       </c>
-      <c r="D24" s="172" t="s">
+      <c r="D24" s="159" t="s">
         <v>501</v>
       </c>
       <c r="F24" s="100" t="s">
         <v>542</v>
       </c>
-      <c r="G24" s="198" t="s">
+      <c r="G24" s="176" t="s">
         <v>541</v>
       </c>
       <c r="J24" s="103" t="s">
@@ -42249,19 +42251,19 @@
       <c r="K24" s="116" t="s">
         <v>653</v>
       </c>
-      <c r="L24" s="201"/>
-      <c r="N24" s="210" t="s">
+      <c r="L24" s="179"/>
+      <c r="N24" s="211" t="s">
         <v>417</v>
       </c>
-      <c r="O24" s="210"/>
-      <c r="P24" s="190"/>
+      <c r="O24" s="211"/>
+      <c r="P24" s="168"/>
       <c r="R24" s="122" t="s">
         <v>460</v>
       </c>
       <c r="S24" s="123" t="s">
         <v>137</v>
       </c>
-      <c r="T24" s="208"/>
+      <c r="T24" s="184"/>
       <c r="U24" s="105" t="s">
         <v>563</v>
       </c>
@@ -42270,16 +42272,16 @@
       </c>
     </row>
     <row r="25" spans="1:28">
-      <c r="A25" s="193" t="s">
+      <c r="A25" s="171" t="s">
         <v>315</v>
       </c>
-      <c r="B25" s="195" t="s">
+      <c r="B25" s="173" t="s">
         <v>453</v>
       </c>
-      <c r="C25" s="175" t="s">
+      <c r="C25" s="162" t="s">
         <v>466</v>
       </c>
-      <c r="D25" s="172" t="s">
+      <c r="D25" s="159" t="s">
         <v>512</v>
       </c>
       <c r="F25" s="102" t="s">
@@ -42294,21 +42296,21 @@
       <c r="K25" s="116" t="s">
         <v>649</v>
       </c>
-      <c r="L25" s="201"/>
-      <c r="N25" s="205" t="s">
+      <c r="L25" s="179"/>
+      <c r="N25" s="181" t="s">
         <v>422</v>
       </c>
-      <c r="O25" s="185" t="s">
+      <c r="O25" s="163" t="s">
         <v>423</v>
       </c>
-      <c r="P25" s="165"/>
+      <c r="P25" s="153"/>
       <c r="R25" s="122" t="s">
         <v>466</v>
       </c>
       <c r="S25" s="123" t="s">
         <v>150</v>
       </c>
-      <c r="T25" s="208"/>
+      <c r="T25" s="184"/>
       <c r="U25" s="105" t="s">
         <v>570</v>
       </c>
@@ -42317,16 +42319,16 @@
       </c>
     </row>
     <row r="26" spans="1:28">
-      <c r="A26" s="193" t="s">
+      <c r="A26" s="171" t="s">
         <v>325</v>
       </c>
-      <c r="B26" s="195" t="s">
+      <c r="B26" s="173" t="s">
         <v>429</v>
       </c>
-      <c r="C26" s="175" t="s">
+      <c r="C26" s="162" t="s">
         <v>430</v>
       </c>
-      <c r="D26" s="172" t="s">
+      <c r="D26" s="159" t="s">
         <v>512</v>
       </c>
       <c r="F26" s="102" t="s">
@@ -42341,21 +42343,21 @@
       <c r="K26" s="116" t="s">
         <v>658</v>
       </c>
-      <c r="L26" s="201"/>
-      <c r="N26" s="206" t="s">
+      <c r="L26" s="179"/>
+      <c r="N26" s="182" t="s">
         <v>431</v>
       </c>
-      <c r="O26" s="212" t="s">
+      <c r="O26" s="187" t="s">
         <v>432</v>
       </c>
-      <c r="P26" s="165"/>
+      <c r="P26" s="153"/>
       <c r="R26" s="122" t="s">
         <v>471</v>
       </c>
       <c r="S26" s="123" t="s">
         <v>182</v>
       </c>
-      <c r="T26" s="208"/>
+      <c r="T26" s="184"/>
       <c r="U26" s="105" t="s">
         <v>576</v>
       </c>
@@ -42364,16 +42366,16 @@
       </c>
     </row>
     <row r="27" spans="1:28">
-      <c r="A27" s="193" t="s">
+      <c r="A27" s="171" t="s">
         <v>325</v>
       </c>
-      <c r="B27" s="195" t="s">
+      <c r="B27" s="173" t="s">
         <v>429</v>
       </c>
-      <c r="C27" s="175" t="s">
+      <c r="C27" s="162" t="s">
         <v>430</v>
       </c>
-      <c r="D27" s="172" t="s">
+      <c r="D27" s="159" t="s">
         <v>518</v>
       </c>
       <c r="F27" s="102" t="s">
@@ -42388,21 +42390,21 @@
       <c r="K27" s="116" t="s">
         <v>653</v>
       </c>
-      <c r="L27" s="201"/>
-      <c r="N27" s="207" t="s">
+      <c r="L27" s="179"/>
+      <c r="N27" s="183" t="s">
         <v>437</v>
       </c>
-      <c r="O27" s="212" t="s">
+      <c r="O27" s="187" t="s">
         <v>438</v>
       </c>
-      <c r="P27" s="165"/>
+      <c r="P27" s="153"/>
       <c r="R27" s="122" t="s">
         <v>476</v>
       </c>
       <c r="S27" s="123" t="s">
         <v>229</v>
       </c>
-      <c r="T27" s="208"/>
+      <c r="T27" s="184"/>
       <c r="U27" s="105" t="s">
         <v>582</v>
       </c>
@@ -42411,16 +42413,16 @@
       </c>
     </row>
     <row r="28" spans="1:28">
-      <c r="A28" s="193" t="s">
+      <c r="A28" s="171" t="s">
         <v>325</v>
       </c>
-      <c r="B28" s="195" t="s">
+      <c r="B28" s="173" t="s">
         <v>429</v>
       </c>
-      <c r="C28" s="175" t="s">
+      <c r="C28" s="162" t="s">
         <v>430</v>
       </c>
-      <c r="D28" s="172" t="s">
+      <c r="D28" s="159" t="s">
         <v>512</v>
       </c>
       <c r="F28" s="102" t="s">
@@ -42435,21 +42437,21 @@
       <c r="K28" s="116" t="s">
         <v>667</v>
       </c>
-      <c r="L28" s="201"/>
-      <c r="N28" s="207" t="s">
+      <c r="L28" s="179"/>
+      <c r="N28" s="183" t="s">
         <v>443</v>
       </c>
-      <c r="O28" s="212" t="s">
+      <c r="O28" s="187" t="s">
         <v>444</v>
       </c>
-      <c r="P28" s="165"/>
+      <c r="P28" s="153"/>
       <c r="R28" s="124" t="s">
         <v>481</v>
       </c>
       <c r="S28" s="125" t="s">
         <v>242</v>
       </c>
-      <c r="T28" s="208"/>
+      <c r="T28" s="184"/>
       <c r="U28" s="105" t="s">
         <v>588</v>
       </c>
@@ -42458,16 +42460,16 @@
       </c>
     </row>
     <row r="29" spans="1:28">
-      <c r="A29" s="193" t="s">
+      <c r="A29" s="171" t="s">
         <v>338</v>
       </c>
-      <c r="B29" s="195" t="s">
+      <c r="B29" s="173" t="s">
         <v>429</v>
       </c>
-      <c r="C29" s="175" t="s">
+      <c r="C29" s="162" t="s">
         <v>471</v>
       </c>
-      <c r="D29" s="172" t="s">
+      <c r="D29" s="159" t="s">
         <v>507</v>
       </c>
       <c r="F29" s="102" t="s">
@@ -42476,15 +42478,15 @@
       <c r="G29" s="101" t="s">
         <v>197</v>
       </c>
-      <c r="L29" s="201"/>
-      <c r="N29" s="207" t="s">
+      <c r="L29" s="179"/>
+      <c r="N29" s="183" t="s">
         <v>449</v>
       </c>
-      <c r="O29" s="212" t="s">
+      <c r="O29" s="187" t="s">
         <v>432</v>
       </c>
-      <c r="P29" s="165"/>
-      <c r="T29" s="208"/>
+      <c r="P29" s="153"/>
+      <c r="T29" s="184"/>
       <c r="U29" s="105" t="s">
         <v>594</v>
       </c>
@@ -42493,16 +42495,16 @@
       </c>
     </row>
     <row r="30" spans="1:28">
-      <c r="A30" s="193" t="s">
+      <c r="A30" s="171" t="s">
         <v>338</v>
       </c>
-      <c r="B30" s="195" t="s">
+      <c r="B30" s="173" t="s">
         <v>429</v>
       </c>
-      <c r="C30" s="175" t="s">
+      <c r="C30" s="162" t="s">
         <v>471</v>
       </c>
-      <c r="D30" s="172" t="s">
+      <c r="D30" s="159" t="s">
         <v>501</v>
       </c>
       <c r="F30" s="102" t="s">
@@ -42511,20 +42513,20 @@
       <c r="G30" s="101" t="s">
         <v>234</v>
       </c>
-      <c r="I30" s="155" t="s">
+      <c r="I30" s="188" t="s">
         <v>418</v>
       </c>
-      <c r="J30" s="204"/>
-      <c r="K30" s="204"/>
-      <c r="L30" s="204"/>
-      <c r="N30" s="207" t="s">
+      <c r="J30" s="189"/>
+      <c r="K30" s="189"/>
+      <c r="L30" s="189"/>
+      <c r="N30" s="183" t="s">
         <v>455</v>
       </c>
-      <c r="O30" s="212" t="s">
+      <c r="O30" s="187" t="s">
         <v>456</v>
       </c>
-      <c r="P30" s="165"/>
-      <c r="T30" s="208"/>
+      <c r="P30" s="153"/>
+      <c r="T30" s="184"/>
       <c r="U30" s="105" t="s">
         <v>601</v>
       </c>
@@ -42533,16 +42535,16 @@
       </c>
     </row>
     <row r="31" spans="1:28">
-      <c r="A31" s="193" t="s">
+      <c r="A31" s="171" t="s">
         <v>348</v>
       </c>
-      <c r="B31" s="195" t="s">
+      <c r="B31" s="173" t="s">
         <v>429</v>
       </c>
-      <c r="C31" s="175" t="s">
+      <c r="C31" s="162" t="s">
         <v>466</v>
       </c>
-      <c r="D31" s="172" t="s">
+      <c r="D31" s="159" t="s">
         <v>501</v>
       </c>
       <c r="F31" s="102" t="s">
@@ -42563,14 +42565,14 @@
       <c r="L31" s="139" t="s">
         <v>427</v>
       </c>
-      <c r="N31" s="207" t="s">
+      <c r="N31" s="183" t="s">
         <v>461</v>
       </c>
-      <c r="O31" s="212" t="s">
+      <c r="O31" s="187" t="s">
         <v>462</v>
       </c>
-      <c r="P31" s="165"/>
-      <c r="T31" s="208"/>
+      <c r="P31" s="153"/>
+      <c r="T31" s="184"/>
       <c r="U31" s="105" t="s">
         <v>607</v>
       </c>
@@ -42579,16 +42581,16 @@
       </c>
     </row>
     <row r="32" spans="1:28">
-      <c r="A32" s="193" t="s">
+      <c r="A32" s="171" t="s">
         <v>348</v>
       </c>
-      <c r="B32" s="195" t="s">
+      <c r="B32" s="173" t="s">
         <v>429</v>
       </c>
-      <c r="C32" s="175" t="s">
+      <c r="C32" s="162" t="s">
         <v>466</v>
       </c>
-      <c r="D32" s="172" t="s">
+      <c r="D32" s="159" t="s">
         <v>512</v>
       </c>
       <c r="F32" s="102" t="s">
@@ -42609,14 +42611,14 @@
       <c r="L32" s="144" t="s">
         <v>435</v>
       </c>
-      <c r="N32" s="207" t="s">
+      <c r="N32" s="183" t="s">
         <v>467</v>
       </c>
-      <c r="O32" s="212" t="s">
+      <c r="O32" s="187" t="s">
         <v>432</v>
       </c>
-      <c r="P32" s="165"/>
-      <c r="T32" s="208"/>
+      <c r="P32" s="153"/>
+      <c r="T32" s="184"/>
       <c r="U32" s="105" t="s">
         <v>613</v>
       </c>
@@ -42625,16 +42627,16 @@
       </c>
     </row>
     <row r="33" spans="1:22">
-      <c r="A33" s="193" t="s">
+      <c r="A33" s="171" t="s">
         <v>348</v>
       </c>
-      <c r="B33" s="195" t="s">
+      <c r="B33" s="173" t="s">
         <v>429</v>
       </c>
-      <c r="C33" s="175" t="s">
+      <c r="C33" s="162" t="s">
         <v>466</v>
       </c>
-      <c r="D33" s="172" t="s">
+      <c r="D33" s="159" t="s">
         <v>507</v>
       </c>
       <c r="F33" s="102" t="s">
@@ -42655,14 +42657,14 @@
       <c r="L33" s="144" t="s">
         <v>441</v>
       </c>
-      <c r="N33" s="207" t="s">
+      <c r="N33" s="183" t="s">
         <v>472</v>
       </c>
-      <c r="O33" s="212" t="s">
+      <c r="O33" s="187" t="s">
         <v>462</v>
       </c>
-      <c r="P33" s="165"/>
-      <c r="T33" s="208"/>
+      <c r="P33" s="153"/>
+      <c r="T33" s="184"/>
       <c r="U33" s="105" t="s">
         <v>618</v>
       </c>
@@ -42671,16 +42673,16 @@
       </c>
     </row>
     <row r="34" spans="1:22">
-      <c r="A34" s="193" t="s">
+      <c r="A34" s="171" t="s">
         <v>356</v>
       </c>
-      <c r="B34" s="195" t="s">
+      <c r="B34" s="173" t="s">
         <v>429</v>
       </c>
-      <c r="C34" s="175" t="s">
+      <c r="C34" s="162" t="s">
         <v>430</v>
       </c>
-      <c r="D34" s="172" t="s">
+      <c r="D34" s="159" t="s">
         <v>518</v>
       </c>
       <c r="F34" s="102" t="s">
@@ -42701,14 +42703,14 @@
       <c r="L34" s="144" t="s">
         <v>447</v>
       </c>
-      <c r="N34" s="207" t="s">
+      <c r="N34" s="183" t="s">
         <v>477</v>
       </c>
-      <c r="O34" s="212" t="s">
+      <c r="O34" s="187" t="s">
         <v>456</v>
       </c>
-      <c r="P34" s="165"/>
-      <c r="T34" s="208"/>
+      <c r="P34" s="153"/>
+      <c r="T34" s="184"/>
       <c r="U34" s="105" t="s">
         <v>625</v>
       </c>
@@ -42717,16 +42719,16 @@
       </c>
     </row>
     <row r="35" spans="1:22">
-      <c r="A35" s="193" t="s">
+      <c r="A35" s="171" t="s">
         <v>356</v>
       </c>
-      <c r="B35" s="195" t="s">
+      <c r="B35" s="173" t="s">
         <v>429</v>
       </c>
-      <c r="C35" s="175" t="s">
+      <c r="C35" s="162" t="s">
         <v>430</v>
       </c>
-      <c r="D35" s="172" t="s">
+      <c r="D35" s="159" t="s">
         <v>512</v>
       </c>
       <c r="F35" s="102" t="s">
@@ -42747,14 +42749,14 @@
       <c r="L35" s="144" t="s">
         <v>452</v>
       </c>
-      <c r="N35" s="207" t="s">
+      <c r="N35" s="183" t="s">
         <v>482</v>
       </c>
-      <c r="O35" s="212" t="s">
+      <c r="O35" s="187" t="s">
         <v>483</v>
       </c>
-      <c r="P35" s="165"/>
-      <c r="T35" s="208"/>
+      <c r="P35" s="153"/>
+      <c r="T35" s="184"/>
       <c r="U35" s="105" t="s">
         <v>631</v>
       </c>
@@ -42763,16 +42765,16 @@
       </c>
     </row>
     <row r="36" spans="1:22">
-      <c r="A36" s="193" t="s">
+      <c r="A36" s="171" t="s">
         <v>356</v>
       </c>
-      <c r="B36" s="195" t="s">
+      <c r="B36" s="173" t="s">
         <v>429</v>
       </c>
-      <c r="C36" s="175" t="s">
+      <c r="C36" s="162" t="s">
         <v>430</v>
       </c>
-      <c r="D36" s="172" t="s">
+      <c r="D36" s="159" t="s">
         <v>518</v>
       </c>
       <c r="F36" s="102" t="s">
@@ -42793,14 +42795,14 @@
       <c r="L36" s="144" t="s">
         <v>459</v>
       </c>
-      <c r="N36" s="207" t="s">
+      <c r="N36" s="183" t="s">
         <v>487</v>
       </c>
-      <c r="O36" s="212" t="s">
+      <c r="O36" s="187" t="s">
         <v>488</v>
       </c>
-      <c r="P36" s="165"/>
-      <c r="T36" s="208"/>
+      <c r="P36" s="153"/>
+      <c r="T36" s="184"/>
       <c r="U36" s="105" t="s">
         <v>638</v>
       </c>
@@ -42809,16 +42811,16 @@
       </c>
     </row>
     <row r="37" spans="1:22">
-      <c r="A37" s="193" t="s">
+      <c r="A37" s="171" t="s">
         <v>367</v>
       </c>
-      <c r="B37" s="195" t="s">
+      <c r="B37" s="173" t="s">
         <v>429</v>
       </c>
-      <c r="C37" s="175" t="s">
+      <c r="C37" s="162" t="s">
         <v>476</v>
       </c>
-      <c r="D37" s="172" t="s">
+      <c r="D37" s="159" t="s">
         <v>518</v>
       </c>
       <c r="F37" s="102" t="s">
@@ -42839,14 +42841,14 @@
       <c r="L37" s="144" t="s">
         <v>465</v>
       </c>
-      <c r="N37" s="207" t="s">
+      <c r="N37" s="183" t="s">
         <v>495</v>
       </c>
-      <c r="O37" s="212" t="s">
+      <c r="O37" s="187" t="s">
         <v>496</v>
       </c>
-      <c r="P37" s="165"/>
-      <c r="T37" s="208"/>
+      <c r="P37" s="153"/>
+      <c r="T37" s="184"/>
       <c r="U37" s="105" t="s">
         <v>643</v>
       </c>
@@ -42855,16 +42857,16 @@
       </c>
     </row>
     <row r="38" spans="1:22">
-      <c r="A38" s="193" t="s">
+      <c r="A38" s="171" t="s">
         <v>367</v>
       </c>
-      <c r="B38" s="195" t="s">
+      <c r="B38" s="173" t="s">
         <v>429</v>
       </c>
-      <c r="C38" s="175" t="s">
+      <c r="C38" s="162" t="s">
         <v>476</v>
       </c>
-      <c r="D38" s="172" t="s">
+      <c r="D38" s="159" t="s">
         <v>518</v>
       </c>
       <c r="F38" s="102" t="s">
@@ -42885,14 +42887,14 @@
       <c r="L38" s="144" t="s">
         <v>470</v>
       </c>
-      <c r="N38" s="207" t="s">
+      <c r="N38" s="183" t="s">
         <v>502</v>
       </c>
-      <c r="O38" s="212" t="s">
+      <c r="O38" s="187" t="s">
         <v>503</v>
       </c>
-      <c r="P38" s="165"/>
-      <c r="T38" s="208"/>
+      <c r="P38" s="153"/>
+      <c r="T38" s="184"/>
       <c r="U38" s="105" t="s">
         <v>648</v>
       </c>
@@ -42901,16 +42903,16 @@
       </c>
     </row>
     <row r="39" spans="1:22">
-      <c r="A39" s="193" t="s">
+      <c r="A39" s="171" t="s">
         <v>373</v>
       </c>
-      <c r="B39" s="195" t="s">
+      <c r="B39" s="173" t="s">
         <v>429</v>
       </c>
-      <c r="C39" s="175" t="s">
+      <c r="C39" s="162" t="s">
         <v>481</v>
       </c>
-      <c r="D39" s="172" t="s">
+      <c r="D39" s="159" t="s">
         <v>507</v>
       </c>
       <c r="F39" s="102" t="s">
@@ -42931,13 +42933,13 @@
       <c r="L39" s="144" t="s">
         <v>475</v>
       </c>
-      <c r="N39" s="207" t="s">
+      <c r="N39" s="183" t="s">
         <v>508</v>
       </c>
-      <c r="O39" s="212" t="s">
+      <c r="O39" s="187" t="s">
         <v>509</v>
       </c>
-      <c r="P39" s="165"/>
+      <c r="P39" s="153"/>
       <c r="U39" s="105" t="s">
         <v>652</v>
       </c>
@@ -42946,16 +42948,16 @@
       </c>
     </row>
     <row r="40" spans="1:22">
-      <c r="A40" s="193" t="s">
+      <c r="A40" s="171" t="s">
         <v>373</v>
       </c>
-      <c r="B40" s="195" t="s">
+      <c r="B40" s="173" t="s">
         <v>429</v>
       </c>
-      <c r="C40" s="175" t="s">
+      <c r="C40" s="162" t="s">
         <v>481</v>
       </c>
-      <c r="D40" s="172" t="s">
+      <c r="D40" s="159" t="s">
         <v>512</v>
       </c>
       <c r="F40" s="102" t="s">
@@ -42976,13 +42978,13 @@
       <c r="L40" s="144" t="s">
         <v>480</v>
       </c>
-      <c r="N40" s="207" t="s">
+      <c r="N40" s="183" t="s">
         <v>513</v>
       </c>
-      <c r="O40" s="212" t="s">
+      <c r="O40" s="187" t="s">
         <v>514</v>
       </c>
-      <c r="P40" s="165"/>
+      <c r="P40" s="153"/>
       <c r="U40" s="105" t="s">
         <v>657</v>
       </c>
@@ -42991,16 +42993,16 @@
       </c>
     </row>
     <row r="41" spans="1:22">
-      <c r="A41" s="193" t="s">
+      <c r="A41" s="171" t="s">
         <v>373</v>
       </c>
-      <c r="B41" s="195" t="s">
+      <c r="B41" s="173" t="s">
         <v>429</v>
       </c>
-      <c r="C41" s="175" t="s">
+      <c r="C41" s="162" t="s">
         <v>481</v>
       </c>
-      <c r="D41" s="172" t="s">
+      <c r="D41" s="159" t="s">
         <v>501</v>
       </c>
       <c r="F41" s="102" t="s">
@@ -43021,13 +43023,13 @@
       <c r="L41" s="144" t="s">
         <v>486</v>
       </c>
-      <c r="N41" s="207" t="s">
+      <c r="N41" s="183" t="s">
         <v>519</v>
       </c>
-      <c r="O41" s="212" t="s">
+      <c r="O41" s="187" t="s">
         <v>520</v>
       </c>
-      <c r="P41" s="165"/>
+      <c r="P41" s="153"/>
       <c r="U41" s="105" t="s">
         <v>663</v>
       </c>
@@ -43036,16 +43038,16 @@
       </c>
     </row>
     <row r="42" spans="1:22">
-      <c r="A42" s="193" t="s">
+      <c r="A42" s="171" t="s">
         <v>380</v>
       </c>
-      <c r="B42" s="195" t="s">
+      <c r="B42" s="173" t="s">
         <v>420</v>
       </c>
-      <c r="C42" s="175" t="s">
+      <c r="C42" s="162" t="s">
         <v>430</v>
       </c>
-      <c r="D42" s="172" t="s">
+      <c r="D42" s="159" t="s">
         <v>501</v>
       </c>
       <c r="F42" s="102" t="s">
@@ -43066,13 +43068,13 @@
       <c r="L42" s="144" t="s">
         <v>491</v>
       </c>
-      <c r="N42" s="207" t="s">
+      <c r="N42" s="183" t="s">
         <v>524</v>
       </c>
-      <c r="O42" s="212" t="s">
+      <c r="O42" s="187" t="s">
         <v>525</v>
       </c>
-      <c r="P42" s="165"/>
+      <c r="P42" s="153"/>
       <c r="U42" s="105" t="s">
         <v>666</v>
       </c>
@@ -43081,16 +43083,16 @@
       </c>
     </row>
     <row r="43" spans="1:22">
-      <c r="A43" s="193" t="s">
+      <c r="A43" s="171" t="s">
         <v>380</v>
       </c>
-      <c r="B43" s="195" t="s">
+      <c r="B43" s="173" t="s">
         <v>420</v>
       </c>
-      <c r="C43" s="175" t="s">
+      <c r="C43" s="162" t="s">
         <v>430</v>
       </c>
-      <c r="D43" s="172" t="s">
+      <c r="D43" s="159" t="s">
         <v>501</v>
       </c>
       <c r="F43" s="110" t="s">
@@ -43111,13 +43113,13 @@
       <c r="L43" s="144" t="s">
         <v>498</v>
       </c>
-      <c r="N43" s="207" t="s">
+      <c r="N43" s="183" t="s">
         <v>529</v>
       </c>
-      <c r="O43" s="212" t="s">
+      <c r="O43" s="187" t="s">
         <v>530</v>
       </c>
-      <c r="P43" s="165"/>
+      <c r="P43" s="153"/>
       <c r="U43" s="105" t="s">
         <v>671</v>
       </c>
@@ -43126,19 +43128,19 @@
       </c>
     </row>
     <row r="44" spans="1:22">
-      <c r="A44" s="193" t="s">
+      <c r="A44" s="171" t="s">
         <v>388</v>
       </c>
-      <c r="B44" s="195" t="s">
+      <c r="B44" s="173" t="s">
         <v>429</v>
       </c>
-      <c r="C44" s="175" t="s">
+      <c r="C44" s="162" t="s">
         <v>466</v>
       </c>
-      <c r="D44" s="172" t="s">
+      <c r="D44" s="159" t="s">
         <v>518</v>
       </c>
-      <c r="F44" s="167"/>
+      <c r="F44" s="155"/>
       <c r="I44" s="140" t="s">
         <v>504</v>
       </c>
@@ -43151,13 +43153,13 @@
       <c r="L44" s="144" t="s">
         <v>506</v>
       </c>
-      <c r="N44" s="207" t="s">
+      <c r="N44" s="183" t="s">
         <v>535</v>
       </c>
-      <c r="O44" s="212" t="s">
+      <c r="O44" s="187" t="s">
         <v>536</v>
       </c>
-      <c r="P44" s="165"/>
+      <c r="P44" s="153"/>
       <c r="U44" s="105" t="s">
         <v>673</v>
       </c>
@@ -43166,16 +43168,16 @@
       </c>
     </row>
     <row r="45" spans="1:22">
-      <c r="A45" s="193" t="s">
+      <c r="A45" s="171" t="s">
         <v>388</v>
       </c>
-      <c r="B45" s="195" t="s">
+      <c r="B45" s="173" t="s">
         <v>429</v>
       </c>
-      <c r="C45" s="175" t="s">
+      <c r="C45" s="162" t="s">
         <v>466</v>
       </c>
-      <c r="D45" s="172" t="s">
+      <c r="D45" s="159" t="s">
         <v>507</v>
       </c>
       <c r="I45" s="140" t="s">
@@ -43190,13 +43192,13 @@
       <c r="L45" s="144" t="s">
         <v>511</v>
       </c>
-      <c r="N45" s="207" t="s">
+      <c r="N45" s="183" t="s">
         <v>543</v>
       </c>
-      <c r="O45" s="212" t="s">
+      <c r="O45" s="187" t="s">
         <v>544</v>
       </c>
-      <c r="P45" s="165"/>
+      <c r="P45" s="153"/>
       <c r="U45" s="105" t="s">
         <v>675</v>
       </c>
@@ -43205,16 +43207,16 @@
       </c>
     </row>
     <row r="46" spans="1:22">
-      <c r="A46" s="193" t="s">
+      <c r="A46" s="171" t="s">
         <v>388</v>
       </c>
-      <c r="B46" s="195" t="s">
+      <c r="B46" s="173" t="s">
         <v>429</v>
       </c>
-      <c r="C46" s="175" t="s">
+      <c r="C46" s="162" t="s">
         <v>466</v>
       </c>
-      <c r="D46" s="172" t="s">
+      <c r="D46" s="159" t="s">
         <v>518</v>
       </c>
       <c r="I46" s="140" t="s">
@@ -43229,10 +43231,10 @@
       <c r="L46" s="144" t="s">
         <v>516</v>
       </c>
-      <c r="N46" s="207" t="s">
+      <c r="N46" s="183" t="s">
         <v>553</v>
       </c>
-      <c r="O46" s="212" t="s">
+      <c r="O46" s="187" t="s">
         <v>554</v>
       </c>
       <c r="U46" s="105" t="s">
@@ -43243,16 +43245,16 @@
       </c>
     </row>
     <row r="47" spans="1:22">
-      <c r="A47" s="193" t="s">
+      <c r="A47" s="171" t="s">
         <v>396</v>
       </c>
-      <c r="B47" s="195" t="s">
+      <c r="B47" s="173" t="s">
         <v>429</v>
       </c>
-      <c r="C47" s="175" t="s">
+      <c r="C47" s="162" t="s">
         <v>448</v>
       </c>
-      <c r="D47" s="172" t="s">
+      <c r="D47" s="159" t="s">
         <v>512</v>
       </c>
       <c r="I47" s="140" t="s">
@@ -43267,10 +43269,10 @@
       <c r="L47" s="144" t="s">
         <v>523</v>
       </c>
-      <c r="N47" s="207" t="s">
+      <c r="N47" s="183" t="s">
         <v>560</v>
       </c>
-      <c r="O47" s="212" t="s">
+      <c r="O47" s="187" t="s">
         <v>561</v>
       </c>
       <c r="U47" s="105" t="s">
@@ -43281,16 +43283,16 @@
       </c>
     </row>
     <row r="48" spans="1:22">
-      <c r="A48" s="193" t="s">
+      <c r="A48" s="171" t="s">
         <v>396</v>
       </c>
-      <c r="B48" s="195" t="s">
+      <c r="B48" s="173" t="s">
         <v>429</v>
       </c>
-      <c r="C48" s="175" t="s">
+      <c r="C48" s="162" t="s">
         <v>448</v>
       </c>
-      <c r="D48" s="172" t="s">
+      <c r="D48" s="159" t="s">
         <v>512</v>
       </c>
       <c r="I48" s="140" t="s">
@@ -43305,10 +43307,10 @@
       <c r="L48" s="144" t="s">
         <v>528</v>
       </c>
-      <c r="N48" s="207" t="s">
+      <c r="N48" s="183" t="s">
         <v>566</v>
       </c>
-      <c r="O48" s="212" t="s">
+      <c r="O48" s="187" t="s">
         <v>567</v>
       </c>
       <c r="U48" s="105" t="s">
@@ -43319,16 +43321,16 @@
       </c>
     </row>
     <row r="49" spans="1:22">
-      <c r="A49" s="193" t="s">
+      <c r="A49" s="171" t="s">
         <v>298</v>
       </c>
-      <c r="B49" s="195" t="s">
+      <c r="B49" s="173" t="s">
         <v>415</v>
       </c>
-      <c r="C49" s="175" t="s">
+      <c r="C49" s="162" t="s">
         <v>430</v>
       </c>
-      <c r="D49" s="172" t="s">
+      <c r="D49" s="159" t="s">
         <v>512</v>
       </c>
       <c r="I49" s="140" t="s">
@@ -43343,10 +43345,10 @@
       <c r="L49" s="144" t="s">
         <v>533</v>
       </c>
-      <c r="N49" s="207" t="s">
+      <c r="N49" s="183" t="s">
         <v>573</v>
       </c>
-      <c r="O49" s="212" t="s">
+      <c r="O49" s="187" t="s">
         <v>530</v>
       </c>
       <c r="U49" s="105" t="s">
@@ -43357,16 +43359,16 @@
       </c>
     </row>
     <row r="50" spans="1:22">
-      <c r="A50" s="193" t="s">
+      <c r="A50" s="171" t="s">
         <v>298</v>
       </c>
-      <c r="B50" s="195" t="s">
+      <c r="B50" s="173" t="s">
         <v>415</v>
       </c>
-      <c r="C50" s="175" t="s">
+      <c r="C50" s="162" t="s">
         <v>430</v>
       </c>
-      <c r="D50" s="172" t="s">
+      <c r="D50" s="159" t="s">
         <v>501</v>
       </c>
       <c r="I50" s="140" t="s">
@@ -43381,10 +43383,10 @@
       <c r="L50" s="144" t="s">
         <v>539</v>
       </c>
-      <c r="N50" s="207" t="s">
+      <c r="N50" s="183" t="s">
         <v>579</v>
       </c>
-      <c r="O50" s="212" t="s">
+      <c r="O50" s="187" t="s">
         <v>554</v>
       </c>
       <c r="U50" s="105" t="s">
@@ -43395,16 +43397,16 @@
       </c>
     </row>
     <row r="51" spans="1:22">
-      <c r="A51" s="193" t="s">
+      <c r="A51" s="171" t="s">
         <v>298</v>
       </c>
-      <c r="B51" s="195" t="s">
+      <c r="B51" s="173" t="s">
         <v>415</v>
       </c>
-      <c r="C51" s="175" t="s">
+      <c r="C51" s="162" t="s">
         <v>430</v>
       </c>
-      <c r="D51" s="172" t="s">
+      <c r="D51" s="159" t="s">
         <v>512</v>
       </c>
       <c r="I51" s="140" t="s">
@@ -43419,10 +43421,10 @@
       <c r="L51" s="144" t="s">
         <v>546</v>
       </c>
-      <c r="N51" s="207" t="s">
+      <c r="N51" s="183" t="s">
         <v>586</v>
       </c>
-      <c r="O51" s="212" t="s">
+      <c r="O51" s="187" t="s">
         <v>561</v>
       </c>
       <c r="U51" s="105" t="s">
@@ -43445,10 +43447,10 @@
       <c r="L52" s="144" t="s">
         <v>557</v>
       </c>
-      <c r="N52" s="207" t="s">
+      <c r="N52" s="183" t="s">
         <v>591</v>
       </c>
-      <c r="O52" s="212" t="s">
+      <c r="O52" s="187" t="s">
         <v>561</v>
       </c>
     </row>
@@ -43465,10 +43467,10 @@
       <c r="L53" s="144" t="s">
         <v>563</v>
       </c>
-      <c r="N53" s="207" t="s">
+      <c r="N53" s="183" t="s">
         <v>597</v>
       </c>
-      <c r="O53" s="212" t="s">
+      <c r="O53" s="187" t="s">
         <v>598</v>
       </c>
     </row>
@@ -43485,10 +43487,10 @@
       <c r="L54" s="144" t="s">
         <v>570</v>
       </c>
-      <c r="N54" s="207" t="s">
+      <c r="N54" s="183" t="s">
         <v>604</v>
       </c>
-      <c r="O54" s="212" t="s">
+      <c r="O54" s="187" t="s">
         <v>605</v>
       </c>
     </row>
@@ -43505,10 +43507,10 @@
       <c r="L55" s="144" t="s">
         <v>576</v>
       </c>
-      <c r="N55" s="207" t="s">
+      <c r="N55" s="183" t="s">
         <v>610</v>
       </c>
-      <c r="O55" s="212" t="s">
+      <c r="O55" s="187" t="s">
         <v>611</v>
       </c>
     </row>
@@ -43525,10 +43527,10 @@
       <c r="L56" s="144" t="s">
         <v>582</v>
       </c>
-      <c r="N56" s="207" t="s">
+      <c r="N56" s="183" t="s">
         <v>616</v>
       </c>
-      <c r="O56" s="212" t="s">
+      <c r="O56" s="187" t="s">
         <v>605</v>
       </c>
     </row>
@@ -43545,10 +43547,10 @@
       <c r="L57" s="144" t="s">
         <v>588</v>
       </c>
-      <c r="N57" s="207" t="s">
+      <c r="N57" s="183" t="s">
         <v>621</v>
       </c>
-      <c r="O57" s="212" t="s">
+      <c r="O57" s="187" t="s">
         <v>622</v>
       </c>
     </row>
@@ -43565,10 +43567,10 @@
       <c r="L58" s="144" t="s">
         <v>594</v>
       </c>
-      <c r="N58" s="207" t="s">
+      <c r="N58" s="183" t="s">
         <v>628</v>
       </c>
-      <c r="O58" s="212" t="s">
+      <c r="O58" s="187" t="s">
         <v>629</v>
       </c>
     </row>
@@ -43585,10 +43587,10 @@
       <c r="L59" s="144" t="s">
         <v>601</v>
       </c>
-      <c r="N59" s="207" t="s">
+      <c r="N59" s="183" t="s">
         <v>634</v>
       </c>
-      <c r="O59" s="212" t="s">
+      <c r="O59" s="187" t="s">
         <v>635</v>
       </c>
     </row>
@@ -43605,10 +43607,10 @@
       <c r="L60" s="144" t="s">
         <v>607</v>
       </c>
-      <c r="N60" s="207" t="s">
+      <c r="N60" s="183" t="s">
         <v>641</v>
       </c>
-      <c r="O60" s="212" t="s">
+      <c r="O60" s="187" t="s">
         <v>635</v>
       </c>
     </row>
@@ -43625,10 +43627,10 @@
       <c r="L61" s="144" t="s">
         <v>613</v>
       </c>
-      <c r="N61" s="207" t="s">
+      <c r="N61" s="183" t="s">
         <v>646</v>
       </c>
-      <c r="O61" s="212" t="s">
+      <c r="O61" s="187" t="s">
         <v>585</v>
       </c>
     </row>
@@ -43901,17 +43903,18 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="R8:S8"/>
+    <mergeCell ref="J1:K1"/>
     <mergeCell ref="I30:L30"/>
     <mergeCell ref="N24:O24"/>
     <mergeCell ref="U1:V1"/>
     <mergeCell ref="R15:S15"/>
     <mergeCell ref="N1:O1"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="R8:S8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
